--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Downloads/lab-main/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Desktop/연구실 홈페이지/lab-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B34D64CB-6CD1-2949-9C17-11E15F66FC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D92088-558D-444E-BD12-48ABB6F55B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11420" yWindow="2520" windowWidth="24000" windowHeight="14820" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="740" yWindow="1880" windowWidth="38580" windowHeight="24980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,25 @@
     <sheet name="Gallery" sheetId="6" r:id="rId6"/>
     <sheet name="Professor" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="256">
   <si>
     <t>KEE LAB 콘텐츠 관리 엑셀</t>
   </si>
@@ -338,10 +351,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>HRD; Vocational Education Training; Lifelong Learning</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>jihoon.shin.916@gmail.com</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -585,191 +594,100 @@
     <t>박종민</t>
   </si>
   <si>
-    <t>alumni_dr28</t>
-  </si>
-  <si>
     <t>김민정</t>
   </si>
   <si>
     <t>M.A.</t>
   </si>
   <si>
-    <t>alumni_dr29</t>
-  </si>
-  <si>
     <t>김주현</t>
   </si>
   <si>
-    <t>alumni_dr30</t>
-  </si>
-  <si>
     <t>김선복</t>
   </si>
   <si>
-    <t>alumni_dr31</t>
-  </si>
-  <si>
     <t>권순영</t>
   </si>
   <si>
-    <t>alumni_dr32</t>
-  </si>
-  <si>
     <t>박진홍</t>
   </si>
   <si>
-    <t>alumni_dr33</t>
-  </si>
-  <si>
     <t>김선미</t>
   </si>
   <si>
     <t>2008</t>
   </si>
   <si>
-    <t>alumni_dr34</t>
-  </si>
-  <si>
     <t>박혜영</t>
   </si>
   <si>
-    <t>alumni_dr35</t>
-  </si>
-  <si>
     <t>정현수</t>
   </si>
   <si>
-    <t>alumni_dr36</t>
-  </si>
-  <si>
     <t>구자봉</t>
   </si>
   <si>
-    <t>alumni_dr37</t>
-  </si>
-  <si>
     <t>김연희</t>
   </si>
   <si>
-    <t>alumni_dr38</t>
-  </si>
-  <si>
     <t>김영문</t>
   </si>
   <si>
-    <t>alumni_dr39</t>
-  </si>
-  <si>
     <t>신효정</t>
   </si>
   <si>
-    <t>alumni_dr40</t>
-  </si>
-  <si>
     <t>엄미란</t>
   </si>
   <si>
-    <t>alumni_dr41</t>
-  </si>
-  <si>
     <t>이경희</t>
   </si>
   <si>
-    <t>alumni_dr42</t>
-  </si>
-  <si>
     <t>이선정</t>
   </si>
   <si>
-    <t>alumni_dr43</t>
-  </si>
-  <si>
     <t>김정진</t>
   </si>
   <si>
-    <t>alumni_dr44</t>
-  </si>
-  <si>
-    <t>alumni_dr45</t>
-  </si>
-  <si>
     <t>함수정</t>
   </si>
   <si>
-    <t>alumni_dr46</t>
-  </si>
-  <si>
-    <t>alumni_dr47</t>
-  </si>
-  <si>
     <t>노경남</t>
   </si>
   <si>
-    <t>alumni_dr48</t>
-  </si>
-  <si>
     <t>허현수</t>
   </si>
   <si>
-    <t>alumni_dr49</t>
-  </si>
-  <si>
     <t>고진석</t>
   </si>
   <si>
-    <t>alumni_dr50</t>
-  </si>
-  <si>
     <t>김승현</t>
   </si>
   <si>
-    <t>alumni_dr51</t>
-  </si>
-  <si>
     <t>이민호</t>
   </si>
   <si>
-    <t>alumni_dr52</t>
-  </si>
-  <si>
     <t>임지회</t>
   </si>
   <si>
-    <t>alumni_dr53</t>
-  </si>
-  <si>
     <t>조성현</t>
   </si>
   <si>
-    <t>alumni_dr54</t>
-  </si>
-  <si>
     <t>유다솜</t>
   </si>
   <si>
     <t>2021</t>
   </si>
   <si>
-    <t>alumni_dr55</t>
-  </si>
-  <si>
     <t>김예빈</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
-    <t>alumni_dr56</t>
-  </si>
-  <si>
     <t>신지훈</t>
   </si>
   <si>
     <t>2025</t>
-  </si>
-  <si>
-    <t>Master · Researcher</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>bio</t>
@@ -803,7 +721,34 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>한국대학교육협의회 (재직중)
+    <t>Lifelong Education; Adult &amp; Vocational Education; Global HRD; Career Development &amp; Transition</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>179571233@qq.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Researcher · Master</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>HRD; Vocational Education Training; Education Data Analysis; Lifelong Learning</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wuhan Huaxia University of Technology 영어학과 학사 졸업
+The Education University of Hong Kong 교육학과 석사 졸업
+숭실대학교 일반대학원 평생교육학과 박사 수료</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>세종대학교 공공정책대학원 사회복지학과 석사 졸업
+숭실대학교 일반대학원 평생교육학과 박사 수료</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국대학교육협의회 (2026.09 ~ 재직중)
 외국인 유학생 학습경험 및 대학적응 연구 프로젝트 수행 중
 국제개발협력(ODA) 교육과정 개발 및 수요 분석 프로젝트 참여
 김예빈, 기영화. (2026). 한국 체류 유럽권 교환학생의 전환학습 경험에 관한 내러티브 탐구. 문화교류와 다문화교육, 15(1), 227–251.
@@ -811,23 +756,114 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Lifelong Education; Adult &amp; Vocational Education; Global HRD; Career Development &amp; Transition</t>
+    <t>alumni_ma1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>179571233@qq.com</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>우한화샤이공대학교 영어교육학과 학사 졸업
-홍콩교육대학교 대학원 교육리더십학과 석사 졸업
-숭실대학교 일반대학원 평생교육학과 박사 수료</t>
+    <t>alumni_ma2</t>
+  </si>
+  <si>
+    <t>alumni_ma3</t>
+  </si>
+  <si>
+    <t>alumni_ma4</t>
+  </si>
+  <si>
+    <t>alumni_ma5</t>
+  </si>
+  <si>
+    <t>alumni_ma6</t>
+  </si>
+  <si>
+    <t>alumni_ma7</t>
+  </si>
+  <si>
+    <t>alumni_ma8</t>
+  </si>
+  <si>
+    <t>alumni_ma9</t>
+  </si>
+  <si>
+    <t>alumni_ma10</t>
+  </si>
+  <si>
+    <t>alumni_ma11</t>
+  </si>
+  <si>
+    <t>alumni_ma12</t>
+  </si>
+  <si>
+    <t>alumni_ma13</t>
+  </si>
+  <si>
+    <t>alumni_ma14</t>
+  </si>
+  <si>
+    <t>alumni_ma15</t>
+  </si>
+  <si>
+    <t>alumni_ma16</t>
+  </si>
+  <si>
+    <t>alumni_ma17</t>
+  </si>
+  <si>
+    <t>alumni_ma18</t>
+  </si>
+  <si>
+    <t>alumni_ma19</t>
+  </si>
+  <si>
+    <t>alumni_ma20</t>
+  </si>
+  <si>
+    <t>alumni_ma21</t>
+  </si>
+  <si>
+    <t>alumni_ma22</t>
+  </si>
+  <si>
+    <t>alumni_ma23</t>
+  </si>
+  <si>
+    <t>alumni_ma24</t>
+  </si>
+  <si>
+    <t>alumni_ma25</t>
+  </si>
+  <si>
+    <t>alumni_ma26</t>
+  </si>
+  <si>
+    <t>alumni_ma27</t>
+  </si>
+  <si>
+    <t>alumni_ma28</t>
+  </si>
+  <si>
+    <t>alumni_ma29</t>
+  </si>
+  <si>
+    <t>(주)멀티캠퍼스 삼성청년SW·AI아카데미 교육운영 (2025.02 ~ 재직중)
+(주)데이원컴퍼니 패스트캠퍼스CIC 집체교육사업 Project Manager (2024.07 ~ 2025.01)
+K-시그니처 협력사업 (혁신적 농촌공동체 개발 프로그램 세네갈 연수원 운영과 커리큘럼 개발) 연구지원인력 (2025.03 ~ 2025.06)
+새마을재단 르완다 협동조합 역량강화사업 종료평가와 코트디부아르 시범마을 조성사업 사후평가 참여 (2024.03 ~ 2024.11)
+숭실대학교 교수학습센터 경험학습 최적화를 위한 META 교육학습체계 구축 교과목 개발 참여자 (2023.03 ~ 2024.01)
+기영화, 신지훈. (2026). 새마을 ODA 사업의 농촌연수원 설립 관련 이해관계자 담론구조와 운영에 관한 텍스트 의미연결망 분석: 세네갈 남부 K지역 사례를 중심으로. 사회적경제와 정책연구, 16(3), 73-101.
+신지훈. (2026). 평생교육진흥기본계획과 정책연구 간 직업교육 의제 정합성 분석 [석사학위논문, 숭실대학교].</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>숭실대학교 국제처 유학생 지원 및 관리 (2025.03 ~ 2026.08)
 평생교육 및 성인교육 관련 연구 수행 (2024 ~ 현재)
-외국인 유학생의 대학생활적응 및 고등교육 관련 연구 수행 (2025 ~ 현재)</t>
+외국인 유학생의 대학생활적응 및 고등교육 관련 연구 수행 (2025 ~ 현재)
+양사동, 기영화. (2026). 외국인 유학생 문화적응 과정 탐색. 한국과 세계, 8(1), 277-310.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국창의 인성교육센터 구군인성교육 강의
+박시언, 기영화. (2026). 행동 사건 면담 (BEI)을 활용한 노인주간보호센터 사회복지사의 역량 모델 개발. 한국케어매니지먼트 연구, 59, 117-152.
+박시언, 기영화. (2025). 군 인성교육 외부 강사의 전문성 형성 과정에 관한 근거이론 연구. 인성교육연구, 10(2), 27-61.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -987,12 +1023,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1018,6 +1048,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1258,10 +1294,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="40" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2" ht="30">
       <c r="A2" s="1" t="s">
@@ -1365,20 +1401,20 @@
   <dimension ref="A1:M201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10" style="15" customWidth="1"/>
-    <col min="2" max="2" width="20" style="15" customWidth="1"/>
-    <col min="3" max="3" width="12" style="15" customWidth="1"/>
-    <col min="4" max="4" width="16" style="15" customWidth="1"/>
-    <col min="5" max="5" width="20" style="15" customWidth="1"/>
-    <col min="6" max="6" width="14" style="15" customWidth="1"/>
-    <col min="7" max="7" width="20" style="15" customWidth="1"/>
-    <col min="8" max="8" width="36" style="15" customWidth="1"/>
-    <col min="9" max="9" width="28" style="15" customWidth="1"/>
-    <col min="10" max="10" width="30" style="15" customWidth="1"/>
-    <col min="11" max="11" width="24" style="15" customWidth="1"/>
-    <col min="12" max="12" width="61.1640625" style="15" customWidth="1"/>
-    <col min="13" max="13" width="50" style="15" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="15"/>
+    <col min="1" max="1" width="10" style="13" customWidth="1"/>
+    <col min="2" max="2" width="20" style="13" customWidth="1"/>
+    <col min="3" max="3" width="12" style="13" customWidth="1"/>
+    <col min="4" max="4" width="16" style="13" customWidth="1"/>
+    <col min="5" max="5" width="20" style="13" customWidth="1"/>
+    <col min="6" max="6" width="14" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20" style="13" customWidth="1"/>
+    <col min="8" max="8" width="36" style="13" customWidth="1"/>
+    <col min="9" max="9" width="28" style="13" customWidth="1"/>
+    <col min="10" max="10" width="30" style="13" customWidth="1"/>
+    <col min="11" max="11" width="24" style="13" customWidth="1"/>
+    <col min="12" max="12" width="61.1640625" style="13" customWidth="1"/>
+    <col min="13" max="13" width="50" style="13" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="40" customHeight="1">
@@ -1416,2727 +1452,2735 @@
         <v>32</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16">
-      <c r="A2" s="16" t="b">
+      <c r="A2" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="15">
         <v>10</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17" t="s">
+      <c r="J2" s="15"/>
+      <c r="K2" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="45">
-      <c r="A3" s="16" t="b">
+    <row r="3" spans="1:13" ht="240">
+      <c r="A3" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="15">
         <v>1</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="I3" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="J3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="K3" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="L3" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="90">
+      <c r="A4" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="M3" s="19" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15">
-      <c r="A4" s="16" t="b">
+      <c r="C4" s="18">
+        <v>2</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="18"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="90">
+      <c r="A5" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="20">
-        <v>2</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" s="20" t="s">
+      <c r="B5" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="18">
+        <v>3</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="H4" s="20"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="M4" s="19"/>
-    </row>
-    <row r="5" spans="1:13" ht="45">
-      <c r="A5" s="16" t="b">
+      <c r="H5" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="M5" s="17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="120">
+      <c r="A6" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="20">
-        <v>3</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="L5" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="M5" s="19" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="120">
-      <c r="A6" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" s="20" t="s">
+      <c r="C6" s="18">
+        <v>4</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="20">
-        <v>4</v>
-      </c>
-      <c r="D6" s="20" t="s">
+      <c r="E6" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="F6" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="L6" s="19" t="s">
-        <v>248</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>245</v>
+      <c r="L6" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
+      <c r="A32" s="18"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="20"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="20"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="20"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="20"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="20"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="20"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="20"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="20"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="20"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="20"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="20"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="20"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="20"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="20"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="20"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="20"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="20"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="20"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" s="20"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="20"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="20"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-      <c r="K58" s="20"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" s="20"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60" s="20"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20"/>
-      <c r="K61" s="20"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="18"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="20"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="20"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="20"/>
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-      <c r="K64" s="20"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="20"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="20"/>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="20"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
-      <c r="J66" s="20"/>
-      <c r="K66" s="20"/>
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="20"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="20"/>
-      <c r="K67" s="20"/>
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18"/>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="18"/>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="20"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
-      <c r="K68" s="20"/>
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="20"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-      <c r="K69" s="20"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="20"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="20"/>
-      <c r="K70" s="20"/>
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="20"/>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20"/>
-      <c r="K71" s="20"/>
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="20"/>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20"/>
-      <c r="K72" s="20"/>
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="20"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="20"/>
-      <c r="K73" s="20"/>
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="20"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="20"/>
-      <c r="K74" s="20"/>
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="20"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
-      <c r="J75" s="20"/>
-      <c r="K75" s="20"/>
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="20"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
-      <c r="H76" s="20"/>
-      <c r="I76" s="20"/>
-      <c r="J76" s="20"/>
-      <c r="K76" s="20"/>
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="18"/>
+      <c r="H76" s="18"/>
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="18"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="20"/>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
-      <c r="J77" s="20"/>
-      <c r="K77" s="20"/>
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="20"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
-      <c r="J78" s="20"/>
-      <c r="K78" s="20"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="18"/>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="20"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
-      <c r="J79" s="20"/>
-      <c r="K79" s="20"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="18"/>
+      <c r="H79" s="18"/>
+      <c r="I79" s="18"/>
+      <c r="J79" s="18"/>
+      <c r="K79" s="18"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="20"/>
-      <c r="B80" s="20"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
-      <c r="J80" s="20"/>
-      <c r="K80" s="20"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="18"/>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="20"/>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20"/>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-      <c r="J81" s="20"/>
-      <c r="K81" s="20"/>
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="18"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="18"/>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="20"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20"/>
-      <c r="H82" s="20"/>
-      <c r="I82" s="20"/>
-      <c r="J82" s="20"/>
-      <c r="K82" s="20"/>
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="18"/>
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+      <c r="K82" s="18"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="20"/>
-      <c r="B83" s="20"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-      <c r="J83" s="20"/>
-      <c r="K83" s="20"/>
+      <c r="A83" s="18"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="18"/>
+      <c r="H83" s="18"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+      <c r="K83" s="18"/>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="20"/>
-      <c r="B84" s="20"/>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
-      <c r="J84" s="20"/>
-      <c r="K84" s="20"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="18"/>
+      <c r="H84" s="18"/>
+      <c r="I84" s="18"/>
+      <c r="J84" s="18"/>
+      <c r="K84" s="18"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="20"/>
-      <c r="B85" s="20"/>
-      <c r="C85" s="20"/>
-      <c r="D85" s="20"/>
-      <c r="E85" s="20"/>
-      <c r="F85" s="20"/>
-      <c r="G85" s="20"/>
-      <c r="H85" s="20"/>
-      <c r="I85" s="20"/>
-      <c r="J85" s="20"/>
-      <c r="K85" s="20"/>
+      <c r="A85" s="18"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="18"/>
+      <c r="H85" s="18"/>
+      <c r="I85" s="18"/>
+      <c r="J85" s="18"/>
+      <c r="K85" s="18"/>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" s="20"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-      <c r="J86" s="20"/>
-      <c r="K86" s="20"/>
+      <c r="A86" s="18"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="18"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="18"/>
+      <c r="J86" s="18"/>
+      <c r="K86" s="18"/>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="20"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="20"/>
-      <c r="I87" s="20"/>
-      <c r="J87" s="20"/>
-      <c r="K87" s="20"/>
+      <c r="A87" s="18"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="18"/>
+      <c r="H87" s="18"/>
+      <c r="I87" s="18"/>
+      <c r="J87" s="18"/>
+      <c r="K87" s="18"/>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="20"/>
-      <c r="B88" s="20"/>
-      <c r="C88" s="20"/>
-      <c r="D88" s="20"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="20"/>
-      <c r="I88" s="20"/>
-      <c r="J88" s="20"/>
-      <c r="K88" s="20"/>
+      <c r="A88" s="18"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="18"/>
+      <c r="E88" s="18"/>
+      <c r="F88" s="18"/>
+      <c r="G88" s="18"/>
+      <c r="H88" s="18"/>
+      <c r="I88" s="18"/>
+      <c r="J88" s="18"/>
+      <c r="K88" s="18"/>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="20"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="20"/>
-      <c r="D89" s="20"/>
-      <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
-      <c r="G89" s="20"/>
-      <c r="H89" s="20"/>
-      <c r="I89" s="20"/>
-      <c r="J89" s="20"/>
-      <c r="K89" s="20"/>
+      <c r="A89" s="18"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="18"/>
+      <c r="G89" s="18"/>
+      <c r="H89" s="18"/>
+      <c r="I89" s="18"/>
+      <c r="J89" s="18"/>
+      <c r="K89" s="18"/>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="20"/>
-      <c r="B90" s="20"/>
-      <c r="C90" s="20"/>
-      <c r="D90" s="20"/>
-      <c r="E90" s="20"/>
-      <c r="F90" s="20"/>
-      <c r="G90" s="20"/>
-      <c r="H90" s="20"/>
-      <c r="I90" s="20"/>
-      <c r="J90" s="20"/>
-      <c r="K90" s="20"/>
+      <c r="A90" s="18"/>
+      <c r="B90" s="18"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="18"/>
+      <c r="E90" s="18"/>
+      <c r="F90" s="18"/>
+      <c r="G90" s="18"/>
+      <c r="H90" s="18"/>
+      <c r="I90" s="18"/>
+      <c r="J90" s="18"/>
+      <c r="K90" s="18"/>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="20"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20"/>
-      <c r="E91" s="20"/>
-      <c r="F91" s="20"/>
-      <c r="G91" s="20"/>
-      <c r="H91" s="20"/>
-      <c r="I91" s="20"/>
-      <c r="J91" s="20"/>
-      <c r="K91" s="20"/>
+      <c r="A91" s="18"/>
+      <c r="B91" s="18"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="18"/>
+      <c r="E91" s="18"/>
+      <c r="F91" s="18"/>
+      <c r="G91" s="18"/>
+      <c r="H91" s="18"/>
+      <c r="I91" s="18"/>
+      <c r="J91" s="18"/>
+      <c r="K91" s="18"/>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="20"/>
-      <c r="B92" s="20"/>
-      <c r="C92" s="20"/>
-      <c r="D92" s="20"/>
-      <c r="E92" s="20"/>
-      <c r="F92" s="20"/>
-      <c r="G92" s="20"/>
-      <c r="H92" s="20"/>
-      <c r="I92" s="20"/>
-      <c r="J92" s="20"/>
-      <c r="K92" s="20"/>
+      <c r="A92" s="18"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="18"/>
+      <c r="D92" s="18"/>
+      <c r="E92" s="18"/>
+      <c r="F92" s="18"/>
+      <c r="G92" s="18"/>
+      <c r="H92" s="18"/>
+      <c r="I92" s="18"/>
+      <c r="J92" s="18"/>
+      <c r="K92" s="18"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="20"/>
-      <c r="B93" s="20"/>
-      <c r="C93" s="20"/>
-      <c r="D93" s="20"/>
-      <c r="E93" s="20"/>
-      <c r="F93" s="20"/>
-      <c r="G93" s="20"/>
-      <c r="H93" s="20"/>
-      <c r="I93" s="20"/>
-      <c r="J93" s="20"/>
-      <c r="K93" s="20"/>
+      <c r="A93" s="18"/>
+      <c r="B93" s="18"/>
+      <c r="C93" s="18"/>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18"/>
+      <c r="F93" s="18"/>
+      <c r="G93" s="18"/>
+      <c r="H93" s="18"/>
+      <c r="I93" s="18"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="18"/>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="20"/>
-      <c r="B94" s="20"/>
-      <c r="C94" s="20"/>
-      <c r="D94" s="20"/>
-      <c r="E94" s="20"/>
-      <c r="F94" s="20"/>
-      <c r="G94" s="20"/>
-      <c r="H94" s="20"/>
-      <c r="I94" s="20"/>
-      <c r="J94" s="20"/>
-      <c r="K94" s="20"/>
+      <c r="A94" s="18"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="18"/>
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
+      <c r="H94" s="18"/>
+      <c r="I94" s="18"/>
+      <c r="J94" s="18"/>
+      <c r="K94" s="18"/>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="20"/>
-      <c r="B95" s="20"/>
-      <c r="C95" s="20"/>
-      <c r="D95" s="20"/>
-      <c r="E95" s="20"/>
-      <c r="F95" s="20"/>
-      <c r="G95" s="20"/>
-      <c r="H95" s="20"/>
-      <c r="I95" s="20"/>
-      <c r="J95" s="20"/>
-      <c r="K95" s="20"/>
+      <c r="A95" s="18"/>
+      <c r="B95" s="18"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="18"/>
+      <c r="E95" s="18"/>
+      <c r="F95" s="18"/>
+      <c r="G95" s="18"/>
+      <c r="H95" s="18"/>
+      <c r="I95" s="18"/>
+      <c r="J95" s="18"/>
+      <c r="K95" s="18"/>
     </row>
     <row r="96" spans="1:11">
-      <c r="A96" s="20"/>
-      <c r="B96" s="20"/>
-      <c r="C96" s="20"/>
-      <c r="D96" s="20"/>
-      <c r="E96" s="20"/>
-      <c r="F96" s="20"/>
-      <c r="G96" s="20"/>
-      <c r="H96" s="20"/>
-      <c r="I96" s="20"/>
-      <c r="J96" s="20"/>
-      <c r="K96" s="20"/>
+      <c r="A96" s="18"/>
+      <c r="B96" s="18"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="18"/>
+      <c r="E96" s="18"/>
+      <c r="F96" s="18"/>
+      <c r="G96" s="18"/>
+      <c r="H96" s="18"/>
+      <c r="I96" s="18"/>
+      <c r="J96" s="18"/>
+      <c r="K96" s="18"/>
     </row>
     <row r="97" spans="1:11">
-      <c r="A97" s="20"/>
-      <c r="B97" s="20"/>
-      <c r="C97" s="20"/>
-      <c r="D97" s="20"/>
-      <c r="E97" s="20"/>
-      <c r="F97" s="20"/>
-      <c r="G97" s="20"/>
-      <c r="H97" s="20"/>
-      <c r="I97" s="20"/>
-      <c r="J97" s="20"/>
-      <c r="K97" s="20"/>
+      <c r="A97" s="18"/>
+      <c r="B97" s="18"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18"/>
+      <c r="E97" s="18"/>
+      <c r="F97" s="18"/>
+      <c r="G97" s="18"/>
+      <c r="H97" s="18"/>
+      <c r="I97" s="18"/>
+      <c r="J97" s="18"/>
+      <c r="K97" s="18"/>
     </row>
     <row r="98" spans="1:11">
-      <c r="A98" s="20"/>
-      <c r="B98" s="20"/>
-      <c r="C98" s="20"/>
-      <c r="D98" s="20"/>
-      <c r="E98" s="20"/>
-      <c r="F98" s="20"/>
-      <c r="G98" s="20"/>
-      <c r="H98" s="20"/>
-      <c r="I98" s="20"/>
-      <c r="J98" s="20"/>
-      <c r="K98" s="20"/>
+      <c r="A98" s="18"/>
+      <c r="B98" s="18"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="18"/>
+      <c r="E98" s="18"/>
+      <c r="F98" s="18"/>
+      <c r="G98" s="18"/>
+      <c r="H98" s="18"/>
+      <c r="I98" s="18"/>
+      <c r="J98" s="18"/>
+      <c r="K98" s="18"/>
     </row>
     <row r="99" spans="1:11">
-      <c r="A99" s="20"/>
-      <c r="B99" s="20"/>
-      <c r="C99" s="20"/>
-      <c r="D99" s="20"/>
-      <c r="E99" s="20"/>
-      <c r="F99" s="20"/>
-      <c r="G99" s="20"/>
-      <c r="H99" s="20"/>
-      <c r="I99" s="20"/>
-      <c r="J99" s="20"/>
-      <c r="K99" s="20"/>
+      <c r="A99" s="18"/>
+      <c r="B99" s="18"/>
+      <c r="C99" s="18"/>
+      <c r="D99" s="18"/>
+      <c r="E99" s="18"/>
+      <c r="F99" s="18"/>
+      <c r="G99" s="18"/>
+      <c r="H99" s="18"/>
+      <c r="I99" s="18"/>
+      <c r="J99" s="18"/>
+      <c r="K99" s="18"/>
     </row>
     <row r="100" spans="1:11">
-      <c r="A100" s="20"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="20"/>
-      <c r="D100" s="20"/>
-      <c r="E100" s="20"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="20"/>
-      <c r="J100" s="20"/>
-      <c r="K100" s="20"/>
+      <c r="A100" s="18"/>
+      <c r="B100" s="18"/>
+      <c r="C100" s="18"/>
+      <c r="D100" s="18"/>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18"/>
+      <c r="G100" s="18"/>
+      <c r="H100" s="18"/>
+      <c r="I100" s="18"/>
+      <c r="J100" s="18"/>
+      <c r="K100" s="18"/>
     </row>
     <row r="101" spans="1:11">
-      <c r="A101" s="20"/>
-      <c r="B101" s="20"/>
-      <c r="C101" s="20"/>
-      <c r="D101" s="20"/>
-      <c r="E101" s="20"/>
-      <c r="F101" s="20"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="20"/>
-      <c r="I101" s="20"/>
-      <c r="J101" s="20"/>
-      <c r="K101" s="20"/>
+      <c r="A101" s="18"/>
+      <c r="B101" s="18"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="18"/>
+      <c r="F101" s="18"/>
+      <c r="G101" s="18"/>
+      <c r="H101" s="18"/>
+      <c r="I101" s="18"/>
+      <c r="J101" s="18"/>
+      <c r="K101" s="18"/>
     </row>
     <row r="102" spans="1:11">
-      <c r="A102" s="20"/>
-      <c r="B102" s="20"/>
-      <c r="C102" s="20"/>
-      <c r="D102" s="20"/>
-      <c r="E102" s="20"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
-      <c r="J102" s="20"/>
-      <c r="K102" s="20"/>
+      <c r="A102" s="18"/>
+      <c r="B102" s="18"/>
+      <c r="C102" s="18"/>
+      <c r="D102" s="18"/>
+      <c r="E102" s="18"/>
+      <c r="F102" s="18"/>
+      <c r="G102" s="18"/>
+      <c r="H102" s="18"/>
+      <c r="I102" s="18"/>
+      <c r="J102" s="18"/>
+      <c r="K102" s="18"/>
     </row>
     <row r="103" spans="1:11">
-      <c r="A103" s="20"/>
-      <c r="B103" s="20"/>
-      <c r="C103" s="20"/>
-      <c r="D103" s="20"/>
-      <c r="E103" s="20"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="20"/>
-      <c r="J103" s="20"/>
-      <c r="K103" s="20"/>
+      <c r="A103" s="18"/>
+      <c r="B103" s="18"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="18"/>
+      <c r="E103" s="18"/>
+      <c r="F103" s="18"/>
+      <c r="G103" s="18"/>
+      <c r="H103" s="18"/>
+      <c r="I103" s="18"/>
+      <c r="J103" s="18"/>
+      <c r="K103" s="18"/>
     </row>
     <row r="104" spans="1:11">
-      <c r="A104" s="20"/>
-      <c r="B104" s="20"/>
-      <c r="C104" s="20"/>
-      <c r="D104" s="20"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="20"/>
-      <c r="G104" s="20"/>
-      <c r="H104" s="20"/>
-      <c r="I104" s="20"/>
-      <c r="J104" s="20"/>
-      <c r="K104" s="20"/>
+      <c r="A104" s="18"/>
+      <c r="B104" s="18"/>
+      <c r="C104" s="18"/>
+      <c r="D104" s="18"/>
+      <c r="E104" s="18"/>
+      <c r="F104" s="18"/>
+      <c r="G104" s="18"/>
+      <c r="H104" s="18"/>
+      <c r="I104" s="18"/>
+      <c r="J104" s="18"/>
+      <c r="K104" s="18"/>
     </row>
     <row r="105" spans="1:11">
-      <c r="A105" s="20"/>
-      <c r="B105" s="20"/>
-      <c r="C105" s="20"/>
-      <c r="D105" s="20"/>
-      <c r="E105" s="20"/>
-      <c r="F105" s="20"/>
-      <c r="G105" s="20"/>
-      <c r="H105" s="20"/>
-      <c r="I105" s="20"/>
-      <c r="J105" s="20"/>
-      <c r="K105" s="20"/>
+      <c r="A105" s="18"/>
+      <c r="B105" s="18"/>
+      <c r="C105" s="18"/>
+      <c r="D105" s="18"/>
+      <c r="E105" s="18"/>
+      <c r="F105" s="18"/>
+      <c r="G105" s="18"/>
+      <c r="H105" s="18"/>
+      <c r="I105" s="18"/>
+      <c r="J105" s="18"/>
+      <c r="K105" s="18"/>
     </row>
     <row r="106" spans="1:11">
-      <c r="A106" s="20"/>
-      <c r="B106" s="20"/>
-      <c r="C106" s="20"/>
-      <c r="D106" s="20"/>
-      <c r="E106" s="20"/>
-      <c r="F106" s="20"/>
-      <c r="G106" s="20"/>
-      <c r="H106" s="20"/>
-      <c r="I106" s="20"/>
-      <c r="J106" s="20"/>
-      <c r="K106" s="20"/>
+      <c r="A106" s="18"/>
+      <c r="B106" s="18"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="18"/>
+      <c r="E106" s="18"/>
+      <c r="F106" s="18"/>
+      <c r="G106" s="18"/>
+      <c r="H106" s="18"/>
+      <c r="I106" s="18"/>
+      <c r="J106" s="18"/>
+      <c r="K106" s="18"/>
     </row>
     <row r="107" spans="1:11">
-      <c r="A107" s="20"/>
-      <c r="B107" s="20"/>
-      <c r="C107" s="20"/>
-      <c r="D107" s="20"/>
-      <c r="E107" s="20"/>
-      <c r="F107" s="20"/>
-      <c r="G107" s="20"/>
-      <c r="H107" s="20"/>
-      <c r="I107" s="20"/>
-      <c r="J107" s="20"/>
-      <c r="K107" s="20"/>
+      <c r="A107" s="18"/>
+      <c r="B107" s="18"/>
+      <c r="C107" s="18"/>
+      <c r="D107" s="18"/>
+      <c r="E107" s="18"/>
+      <c r="F107" s="18"/>
+      <c r="G107" s="18"/>
+      <c r="H107" s="18"/>
+      <c r="I107" s="18"/>
+      <c r="J107" s="18"/>
+      <c r="K107" s="18"/>
     </row>
     <row r="108" spans="1:11">
-      <c r="A108" s="20"/>
-      <c r="B108" s="20"/>
-      <c r="C108" s="20"/>
-      <c r="D108" s="20"/>
-      <c r="E108" s="20"/>
-      <c r="F108" s="20"/>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
-      <c r="J108" s="20"/>
-      <c r="K108" s="20"/>
+      <c r="A108" s="18"/>
+      <c r="B108" s="18"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18"/>
+      <c r="I108" s="18"/>
+      <c r="J108" s="18"/>
+      <c r="K108" s="18"/>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" s="20"/>
-      <c r="B109" s="20"/>
-      <c r="C109" s="20"/>
-      <c r="D109" s="20"/>
-      <c r="E109" s="20"/>
-      <c r="F109" s="20"/>
-      <c r="G109" s="20"/>
-      <c r="H109" s="20"/>
-      <c r="I109" s="20"/>
-      <c r="J109" s="20"/>
-      <c r="K109" s="20"/>
+      <c r="A109" s="18"/>
+      <c r="B109" s="18"/>
+      <c r="C109" s="18"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18"/>
+      <c r="I109" s="18"/>
+      <c r="J109" s="18"/>
+      <c r="K109" s="18"/>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" s="20"/>
-      <c r="B110" s="20"/>
-      <c r="C110" s="20"/>
-      <c r="D110" s="20"/>
-      <c r="E110" s="20"/>
-      <c r="F110" s="20"/>
-      <c r="G110" s="20"/>
-      <c r="H110" s="20"/>
-      <c r="I110" s="20"/>
-      <c r="J110" s="20"/>
-      <c r="K110" s="20"/>
+      <c r="A110" s="18"/>
+      <c r="B110" s="18"/>
+      <c r="C110" s="18"/>
+      <c r="D110" s="18"/>
+      <c r="E110" s="18"/>
+      <c r="F110" s="18"/>
+      <c r="G110" s="18"/>
+      <c r="H110" s="18"/>
+      <c r="I110" s="18"/>
+      <c r="J110" s="18"/>
+      <c r="K110" s="18"/>
     </row>
     <row r="111" spans="1:11">
-      <c r="A111" s="20"/>
-      <c r="B111" s="20"/>
-      <c r="C111" s="20"/>
-      <c r="D111" s="20"/>
-      <c r="E111" s="20"/>
-      <c r="F111" s="20"/>
-      <c r="G111" s="20"/>
-      <c r="H111" s="20"/>
-      <c r="I111" s="20"/>
-      <c r="J111" s="20"/>
-      <c r="K111" s="20"/>
+      <c r="A111" s="18"/>
+      <c r="B111" s="18"/>
+      <c r="C111" s="18"/>
+      <c r="D111" s="18"/>
+      <c r="E111" s="18"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
+      <c r="H111" s="18"/>
+      <c r="I111" s="18"/>
+      <c r="J111" s="18"/>
+      <c r="K111" s="18"/>
     </row>
     <row r="112" spans="1:11">
-      <c r="A112" s="20"/>
-      <c r="B112" s="20"/>
-      <c r="C112" s="20"/>
-      <c r="D112" s="20"/>
-      <c r="E112" s="20"/>
-      <c r="F112" s="20"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
-      <c r="I112" s="20"/>
-      <c r="J112" s="20"/>
-      <c r="K112" s="20"/>
+      <c r="A112" s="18"/>
+      <c r="B112" s="18"/>
+      <c r="C112" s="18"/>
+      <c r="D112" s="18"/>
+      <c r="E112" s="18"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18"/>
+      <c r="I112" s="18"/>
+      <c r="J112" s="18"/>
+      <c r="K112" s="18"/>
     </row>
     <row r="113" spans="1:11">
-      <c r="A113" s="20"/>
-      <c r="B113" s="20"/>
-      <c r="C113" s="20"/>
-      <c r="D113" s="20"/>
-      <c r="E113" s="20"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="20"/>
-      <c r="J113" s="20"/>
-      <c r="K113" s="20"/>
+      <c r="A113" s="18"/>
+      <c r="B113" s="18"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="18"/>
+      <c r="J113" s="18"/>
+      <c r="K113" s="18"/>
     </row>
     <row r="114" spans="1:11">
-      <c r="A114" s="20"/>
-      <c r="B114" s="20"/>
-      <c r="C114" s="20"/>
-      <c r="D114" s="20"/>
-      <c r="E114" s="20"/>
-      <c r="F114" s="20"/>
-      <c r="G114" s="20"/>
-      <c r="H114" s="20"/>
-      <c r="I114" s="20"/>
-      <c r="J114" s="20"/>
-      <c r="K114" s="20"/>
+      <c r="A114" s="18"/>
+      <c r="B114" s="18"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="18"/>
+      <c r="J114" s="18"/>
+      <c r="K114" s="18"/>
     </row>
     <row r="115" spans="1:11">
-      <c r="A115" s="20"/>
-      <c r="B115" s="20"/>
-      <c r="C115" s="20"/>
-      <c r="D115" s="20"/>
-      <c r="E115" s="20"/>
-      <c r="F115" s="20"/>
-      <c r="G115" s="20"/>
-      <c r="H115" s="20"/>
-      <c r="I115" s="20"/>
-      <c r="J115" s="20"/>
-      <c r="K115" s="20"/>
+      <c r="A115" s="18"/>
+      <c r="B115" s="18"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="18"/>
+      <c r="G115" s="18"/>
+      <c r="H115" s="18"/>
+      <c r="I115" s="18"/>
+      <c r="J115" s="18"/>
+      <c r="K115" s="18"/>
     </row>
     <row r="116" spans="1:11">
-      <c r="A116" s="20"/>
-      <c r="B116" s="20"/>
-      <c r="C116" s="20"/>
-      <c r="D116" s="20"/>
-      <c r="E116" s="20"/>
-      <c r="F116" s="20"/>
-      <c r="G116" s="20"/>
-      <c r="H116" s="20"/>
-      <c r="I116" s="20"/>
-      <c r="J116" s="20"/>
-      <c r="K116" s="20"/>
+      <c r="A116" s="18"/>
+      <c r="B116" s="18"/>
+      <c r="C116" s="18"/>
+      <c r="D116" s="18"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="18"/>
+      <c r="G116" s="18"/>
+      <c r="H116" s="18"/>
+      <c r="I116" s="18"/>
+      <c r="J116" s="18"/>
+      <c r="K116" s="18"/>
     </row>
     <row r="117" spans="1:11">
-      <c r="A117" s="20"/>
-      <c r="B117" s="20"/>
-      <c r="C117" s="20"/>
-      <c r="D117" s="20"/>
-      <c r="E117" s="20"/>
-      <c r="F117" s="20"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
-      <c r="I117" s="20"/>
-      <c r="J117" s="20"/>
-      <c r="K117" s="20"/>
+      <c r="A117" s="18"/>
+      <c r="B117" s="18"/>
+      <c r="C117" s="18"/>
+      <c r="D117" s="18"/>
+      <c r="E117" s="18"/>
+      <c r="F117" s="18"/>
+      <c r="G117" s="18"/>
+      <c r="H117" s="18"/>
+      <c r="I117" s="18"/>
+      <c r="J117" s="18"/>
+      <c r="K117" s="18"/>
     </row>
     <row r="118" spans="1:11">
-      <c r="A118" s="20"/>
-      <c r="B118" s="20"/>
-      <c r="C118" s="20"/>
-      <c r="D118" s="20"/>
-      <c r="E118" s="20"/>
-      <c r="F118" s="20"/>
-      <c r="G118" s="20"/>
-      <c r="H118" s="20"/>
-      <c r="I118" s="20"/>
-      <c r="J118" s="20"/>
-      <c r="K118" s="20"/>
+      <c r="A118" s="18"/>
+      <c r="B118" s="18"/>
+      <c r="C118" s="18"/>
+      <c r="D118" s="18"/>
+      <c r="E118" s="18"/>
+      <c r="F118" s="18"/>
+      <c r="G118" s="18"/>
+      <c r="H118" s="18"/>
+      <c r="I118" s="18"/>
+      <c r="J118" s="18"/>
+      <c r="K118" s="18"/>
     </row>
     <row r="119" spans="1:11">
-      <c r="A119" s="20"/>
-      <c r="B119" s="20"/>
-      <c r="C119" s="20"/>
-      <c r="D119" s="20"/>
-      <c r="E119" s="20"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="20"/>
-      <c r="I119" s="20"/>
-      <c r="J119" s="20"/>
-      <c r="K119" s="20"/>
+      <c r="A119" s="18"/>
+      <c r="B119" s="18"/>
+      <c r="C119" s="18"/>
+      <c r="D119" s="18"/>
+      <c r="E119" s="18"/>
+      <c r="F119" s="18"/>
+      <c r="G119" s="18"/>
+      <c r="H119" s="18"/>
+      <c r="I119" s="18"/>
+      <c r="J119" s="18"/>
+      <c r="K119" s="18"/>
     </row>
     <row r="120" spans="1:11">
-      <c r="A120" s="20"/>
-      <c r="B120" s="20"/>
-      <c r="C120" s="20"/>
-      <c r="D120" s="20"/>
-      <c r="E120" s="20"/>
-      <c r="F120" s="20"/>
-      <c r="G120" s="20"/>
-      <c r="H120" s="20"/>
-      <c r="I120" s="20"/>
-      <c r="J120" s="20"/>
-      <c r="K120" s="20"/>
+      <c r="A120" s="18"/>
+      <c r="B120" s="18"/>
+      <c r="C120" s="18"/>
+      <c r="D120" s="18"/>
+      <c r="E120" s="18"/>
+      <c r="F120" s="18"/>
+      <c r="G120" s="18"/>
+      <c r="H120" s="18"/>
+      <c r="I120" s="18"/>
+      <c r="J120" s="18"/>
+      <c r="K120" s="18"/>
     </row>
     <row r="121" spans="1:11">
-      <c r="A121" s="20"/>
-      <c r="B121" s="20"/>
-      <c r="C121" s="20"/>
-      <c r="D121" s="20"/>
-      <c r="E121" s="20"/>
-      <c r="F121" s="20"/>
-      <c r="G121" s="20"/>
-      <c r="H121" s="20"/>
-      <c r="I121" s="20"/>
-      <c r="J121" s="20"/>
-      <c r="K121" s="20"/>
+      <c r="A121" s="18"/>
+      <c r="B121" s="18"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="18"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="18"/>
+      <c r="G121" s="18"/>
+      <c r="H121" s="18"/>
+      <c r="I121" s="18"/>
+      <c r="J121" s="18"/>
+      <c r="K121" s="18"/>
     </row>
     <row r="122" spans="1:11">
-      <c r="A122" s="20"/>
-      <c r="B122" s="20"/>
-      <c r="C122" s="20"/>
-      <c r="D122" s="20"/>
-      <c r="E122" s="20"/>
-      <c r="F122" s="20"/>
-      <c r="G122" s="20"/>
-      <c r="H122" s="20"/>
-      <c r="I122" s="20"/>
-      <c r="J122" s="20"/>
-      <c r="K122" s="20"/>
+      <c r="A122" s="18"/>
+      <c r="B122" s="18"/>
+      <c r="C122" s="18"/>
+      <c r="D122" s="18"/>
+      <c r="E122" s="18"/>
+      <c r="F122" s="18"/>
+      <c r="G122" s="18"/>
+      <c r="H122" s="18"/>
+      <c r="I122" s="18"/>
+      <c r="J122" s="18"/>
+      <c r="K122" s="18"/>
     </row>
     <row r="123" spans="1:11">
-      <c r="A123" s="20"/>
-      <c r="B123" s="20"/>
-      <c r="C123" s="20"/>
-      <c r="D123" s="20"/>
-      <c r="E123" s="20"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="20"/>
-      <c r="I123" s="20"/>
-      <c r="J123" s="20"/>
-      <c r="K123" s="20"/>
+      <c r="A123" s="18"/>
+      <c r="B123" s="18"/>
+      <c r="C123" s="18"/>
+      <c r="D123" s="18"/>
+      <c r="E123" s="18"/>
+      <c r="F123" s="18"/>
+      <c r="G123" s="18"/>
+      <c r="H123" s="18"/>
+      <c r="I123" s="18"/>
+      <c r="J123" s="18"/>
+      <c r="K123" s="18"/>
     </row>
     <row r="124" spans="1:11">
-      <c r="A124" s="20"/>
-      <c r="B124" s="20"/>
-      <c r="C124" s="20"/>
-      <c r="D124" s="20"/>
-      <c r="E124" s="20"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
-      <c r="I124" s="20"/>
-      <c r="J124" s="20"/>
-      <c r="K124" s="20"/>
+      <c r="A124" s="18"/>
+      <c r="B124" s="18"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="18"/>
+      <c r="E124" s="18"/>
+      <c r="F124" s="18"/>
+      <c r="G124" s="18"/>
+      <c r="H124" s="18"/>
+      <c r="I124" s="18"/>
+      <c r="J124" s="18"/>
+      <c r="K124" s="18"/>
     </row>
     <row r="125" spans="1:11">
-      <c r="A125" s="20"/>
-      <c r="B125" s="20"/>
-      <c r="C125" s="20"/>
-      <c r="D125" s="20"/>
-      <c r="E125" s="20"/>
-      <c r="F125" s="20"/>
-      <c r="G125" s="20"/>
-      <c r="H125" s="20"/>
-      <c r="I125" s="20"/>
-      <c r="J125" s="20"/>
-      <c r="K125" s="20"/>
+      <c r="A125" s="18"/>
+      <c r="B125" s="18"/>
+      <c r="C125" s="18"/>
+      <c r="D125" s="18"/>
+      <c r="E125" s="18"/>
+      <c r="F125" s="18"/>
+      <c r="G125" s="18"/>
+      <c r="H125" s="18"/>
+      <c r="I125" s="18"/>
+      <c r="J125" s="18"/>
+      <c r="K125" s="18"/>
     </row>
     <row r="126" spans="1:11">
-      <c r="A126" s="20"/>
-      <c r="B126" s="20"/>
-      <c r="C126" s="20"/>
-      <c r="D126" s="20"/>
-      <c r="E126" s="20"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="20"/>
-      <c r="I126" s="20"/>
-      <c r="J126" s="20"/>
-      <c r="K126" s="20"/>
+      <c r="A126" s="18"/>
+      <c r="B126" s="18"/>
+      <c r="C126" s="18"/>
+      <c r="D126" s="18"/>
+      <c r="E126" s="18"/>
+      <c r="F126" s="18"/>
+      <c r="G126" s="18"/>
+      <c r="H126" s="18"/>
+      <c r="I126" s="18"/>
+      <c r="J126" s="18"/>
+      <c r="K126" s="18"/>
     </row>
     <row r="127" spans="1:11">
-      <c r="A127" s="20"/>
-      <c r="B127" s="20"/>
-      <c r="C127" s="20"/>
-      <c r="D127" s="20"/>
-      <c r="E127" s="20"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="20"/>
-      <c r="I127" s="20"/>
-      <c r="J127" s="20"/>
-      <c r="K127" s="20"/>
+      <c r="A127" s="18"/>
+      <c r="B127" s="18"/>
+      <c r="C127" s="18"/>
+      <c r="D127" s="18"/>
+      <c r="E127" s="18"/>
+      <c r="F127" s="18"/>
+      <c r="G127" s="18"/>
+      <c r="H127" s="18"/>
+      <c r="I127" s="18"/>
+      <c r="J127" s="18"/>
+      <c r="K127" s="18"/>
     </row>
     <row r="128" spans="1:11">
-      <c r="A128" s="20"/>
-      <c r="B128" s="20"/>
-      <c r="C128" s="20"/>
-      <c r="D128" s="20"/>
-      <c r="E128" s="20"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="20"/>
-      <c r="I128" s="20"/>
-      <c r="J128" s="20"/>
-      <c r="K128" s="20"/>
+      <c r="A128" s="18"/>
+      <c r="B128" s="18"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="18"/>
+      <c r="E128" s="18"/>
+      <c r="F128" s="18"/>
+      <c r="G128" s="18"/>
+      <c r="H128" s="18"/>
+      <c r="I128" s="18"/>
+      <c r="J128" s="18"/>
+      <c r="K128" s="18"/>
     </row>
     <row r="129" spans="1:11">
-      <c r="A129" s="20"/>
-      <c r="B129" s="20"/>
-      <c r="C129" s="20"/>
-      <c r="D129" s="20"/>
-      <c r="E129" s="20"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
-      <c r="I129" s="20"/>
-      <c r="J129" s="20"/>
-      <c r="K129" s="20"/>
+      <c r="A129" s="18"/>
+      <c r="B129" s="18"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="18"/>
+      <c r="E129" s="18"/>
+      <c r="F129" s="18"/>
+      <c r="G129" s="18"/>
+      <c r="H129" s="18"/>
+      <c r="I129" s="18"/>
+      <c r="J129" s="18"/>
+      <c r="K129" s="18"/>
     </row>
     <row r="130" spans="1:11">
-      <c r="A130" s="20"/>
-      <c r="B130" s="20"/>
-      <c r="C130" s="20"/>
-      <c r="D130" s="20"/>
-      <c r="E130" s="20"/>
-      <c r="F130" s="20"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="20"/>
-      <c r="I130" s="20"/>
-      <c r="J130" s="20"/>
-      <c r="K130" s="20"/>
+      <c r="A130" s="18"/>
+      <c r="B130" s="18"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="18"/>
+      <c r="E130" s="18"/>
+      <c r="F130" s="18"/>
+      <c r="G130" s="18"/>
+      <c r="H130" s="18"/>
+      <c r="I130" s="18"/>
+      <c r="J130" s="18"/>
+      <c r="K130" s="18"/>
     </row>
     <row r="131" spans="1:11">
-      <c r="A131" s="20"/>
-      <c r="B131" s="20"/>
-      <c r="C131" s="20"/>
-      <c r="D131" s="20"/>
-      <c r="E131" s="20"/>
-      <c r="F131" s="20"/>
-      <c r="G131" s="20"/>
-      <c r="H131" s="20"/>
-      <c r="I131" s="20"/>
-      <c r="J131" s="20"/>
-      <c r="K131" s="20"/>
+      <c r="A131" s="18"/>
+      <c r="B131" s="18"/>
+      <c r="C131" s="18"/>
+      <c r="D131" s="18"/>
+      <c r="E131" s="18"/>
+      <c r="F131" s="18"/>
+      <c r="G131" s="18"/>
+      <c r="H131" s="18"/>
+      <c r="I131" s="18"/>
+      <c r="J131" s="18"/>
+      <c r="K131" s="18"/>
     </row>
     <row r="132" spans="1:11">
-      <c r="A132" s="20"/>
-      <c r="B132" s="20"/>
-      <c r="C132" s="20"/>
-      <c r="D132" s="20"/>
-      <c r="E132" s="20"/>
-      <c r="F132" s="20"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="20"/>
-      <c r="I132" s="20"/>
-      <c r="J132" s="20"/>
-      <c r="K132" s="20"/>
+      <c r="A132" s="18"/>
+      <c r="B132" s="18"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="18"/>
+      <c r="G132" s="18"/>
+      <c r="H132" s="18"/>
+      <c r="I132" s="18"/>
+      <c r="J132" s="18"/>
+      <c r="K132" s="18"/>
     </row>
     <row r="133" spans="1:11">
-      <c r="A133" s="20"/>
-      <c r="B133" s="20"/>
-      <c r="C133" s="20"/>
-      <c r="D133" s="20"/>
-      <c r="E133" s="20"/>
-      <c r="F133" s="20"/>
-      <c r="G133" s="20"/>
-      <c r="H133" s="20"/>
-      <c r="I133" s="20"/>
-      <c r="J133" s="20"/>
-      <c r="K133" s="20"/>
+      <c r="A133" s="18"/>
+      <c r="B133" s="18"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18"/>
+      <c r="G133" s="18"/>
+      <c r="H133" s="18"/>
+      <c r="I133" s="18"/>
+      <c r="J133" s="18"/>
+      <c r="K133" s="18"/>
     </row>
     <row r="134" spans="1:11">
-      <c r="A134" s="20"/>
-      <c r="B134" s="20"/>
-      <c r="C134" s="20"/>
-      <c r="D134" s="20"/>
-      <c r="E134" s="20"/>
-      <c r="F134" s="20"/>
-      <c r="G134" s="20"/>
-      <c r="H134" s="20"/>
-      <c r="I134" s="20"/>
-      <c r="J134" s="20"/>
-      <c r="K134" s="20"/>
+      <c r="A134" s="18"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="18"/>
+      <c r="F134" s="18"/>
+      <c r="G134" s="18"/>
+      <c r="H134" s="18"/>
+      <c r="I134" s="18"/>
+      <c r="J134" s="18"/>
+      <c r="K134" s="18"/>
     </row>
     <row r="135" spans="1:11">
-      <c r="A135" s="20"/>
-      <c r="B135" s="20"/>
-      <c r="C135" s="20"/>
-      <c r="D135" s="20"/>
-      <c r="E135" s="20"/>
-      <c r="F135" s="20"/>
-      <c r="G135" s="20"/>
-      <c r="H135" s="20"/>
-      <c r="I135" s="20"/>
-      <c r="J135" s="20"/>
-      <c r="K135" s="20"/>
+      <c r="A135" s="18"/>
+      <c r="B135" s="18"/>
+      <c r="C135" s="18"/>
+      <c r="D135" s="18"/>
+      <c r="E135" s="18"/>
+      <c r="F135" s="18"/>
+      <c r="G135" s="18"/>
+      <c r="H135" s="18"/>
+      <c r="I135" s="18"/>
+      <c r="J135" s="18"/>
+      <c r="K135" s="18"/>
     </row>
     <row r="136" spans="1:11">
-      <c r="A136" s="20"/>
-      <c r="B136" s="20"/>
-      <c r="C136" s="20"/>
-      <c r="D136" s="20"/>
-      <c r="E136" s="20"/>
-      <c r="F136" s="20"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="20"/>
-      <c r="I136" s="20"/>
-      <c r="J136" s="20"/>
-      <c r="K136" s="20"/>
+      <c r="A136" s="18"/>
+      <c r="B136" s="18"/>
+      <c r="C136" s="18"/>
+      <c r="D136" s="18"/>
+      <c r="E136" s="18"/>
+      <c r="F136" s="18"/>
+      <c r="G136" s="18"/>
+      <c r="H136" s="18"/>
+      <c r="I136" s="18"/>
+      <c r="J136" s="18"/>
+      <c r="K136" s="18"/>
     </row>
     <row r="137" spans="1:11">
-      <c r="A137" s="20"/>
-      <c r="B137" s="20"/>
-      <c r="C137" s="20"/>
-      <c r="D137" s="20"/>
-      <c r="E137" s="20"/>
-      <c r="F137" s="20"/>
-      <c r="G137" s="20"/>
-      <c r="H137" s="20"/>
-      <c r="I137" s="20"/>
-      <c r="J137" s="20"/>
-      <c r="K137" s="20"/>
+      <c r="A137" s="18"/>
+      <c r="B137" s="18"/>
+      <c r="C137" s="18"/>
+      <c r="D137" s="18"/>
+      <c r="E137" s="18"/>
+      <c r="F137" s="18"/>
+      <c r="G137" s="18"/>
+      <c r="H137" s="18"/>
+      <c r="I137" s="18"/>
+      <c r="J137" s="18"/>
+      <c r="K137" s="18"/>
     </row>
     <row r="138" spans="1:11">
-      <c r="A138" s="20"/>
-      <c r="B138" s="20"/>
-      <c r="C138" s="20"/>
-      <c r="D138" s="20"/>
-      <c r="E138" s="20"/>
-      <c r="F138" s="20"/>
-      <c r="G138" s="20"/>
-      <c r="H138" s="20"/>
-      <c r="I138" s="20"/>
-      <c r="J138" s="20"/>
-      <c r="K138" s="20"/>
+      <c r="A138" s="18"/>
+      <c r="B138" s="18"/>
+      <c r="C138" s="18"/>
+      <c r="D138" s="18"/>
+      <c r="E138" s="18"/>
+      <c r="F138" s="18"/>
+      <c r="G138" s="18"/>
+      <c r="H138" s="18"/>
+      <c r="I138" s="18"/>
+      <c r="J138" s="18"/>
+      <c r="K138" s="18"/>
     </row>
     <row r="139" spans="1:11">
-      <c r="A139" s="20"/>
-      <c r="B139" s="20"/>
-      <c r="C139" s="20"/>
-      <c r="D139" s="20"/>
-      <c r="E139" s="20"/>
-      <c r="F139" s="20"/>
-      <c r="G139" s="20"/>
-      <c r="H139" s="20"/>
-      <c r="I139" s="20"/>
-      <c r="J139" s="20"/>
-      <c r="K139" s="20"/>
+      <c r="A139" s="18"/>
+      <c r="B139" s="18"/>
+      <c r="C139" s="18"/>
+      <c r="D139" s="18"/>
+      <c r="E139" s="18"/>
+      <c r="F139" s="18"/>
+      <c r="G139" s="18"/>
+      <c r="H139" s="18"/>
+      <c r="I139" s="18"/>
+      <c r="J139" s="18"/>
+      <c r="K139" s="18"/>
     </row>
     <row r="140" spans="1:11">
-      <c r="A140" s="20"/>
-      <c r="B140" s="20"/>
-      <c r="C140" s="20"/>
-      <c r="D140" s="20"/>
-      <c r="E140" s="20"/>
-      <c r="F140" s="20"/>
-      <c r="G140" s="20"/>
-      <c r="H140" s="20"/>
-      <c r="I140" s="20"/>
-      <c r="J140" s="20"/>
-      <c r="K140" s="20"/>
+      <c r="A140" s="18"/>
+      <c r="B140" s="18"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="18"/>
+      <c r="G140" s="18"/>
+      <c r="H140" s="18"/>
+      <c r="I140" s="18"/>
+      <c r="J140" s="18"/>
+      <c r="K140" s="18"/>
     </row>
     <row r="141" spans="1:11">
-      <c r="A141" s="20"/>
-      <c r="B141" s="20"/>
-      <c r="C141" s="20"/>
-      <c r="D141" s="20"/>
-      <c r="E141" s="20"/>
-      <c r="F141" s="20"/>
-      <c r="G141" s="20"/>
-      <c r="H141" s="20"/>
-      <c r="I141" s="20"/>
-      <c r="J141" s="20"/>
-      <c r="K141" s="20"/>
+      <c r="A141" s="18"/>
+      <c r="B141" s="18"/>
+      <c r="C141" s="18"/>
+      <c r="D141" s="18"/>
+      <c r="E141" s="18"/>
+      <c r="F141" s="18"/>
+      <c r="G141" s="18"/>
+      <c r="H141" s="18"/>
+      <c r="I141" s="18"/>
+      <c r="J141" s="18"/>
+      <c r="K141" s="18"/>
     </row>
     <row r="142" spans="1:11">
-      <c r="A142" s="20"/>
-      <c r="B142" s="20"/>
-      <c r="C142" s="20"/>
-      <c r="D142" s="20"/>
-      <c r="E142" s="20"/>
-      <c r="F142" s="20"/>
-      <c r="G142" s="20"/>
-      <c r="H142" s="20"/>
-      <c r="I142" s="20"/>
-      <c r="J142" s="20"/>
-      <c r="K142" s="20"/>
+      <c r="A142" s="18"/>
+      <c r="B142" s="18"/>
+      <c r="C142" s="18"/>
+      <c r="D142" s="18"/>
+      <c r="E142" s="18"/>
+      <c r="F142" s="18"/>
+      <c r="G142" s="18"/>
+      <c r="H142" s="18"/>
+      <c r="I142" s="18"/>
+      <c r="J142" s="18"/>
+      <c r="K142" s="18"/>
     </row>
     <row r="143" spans="1:11">
-      <c r="A143" s="20"/>
-      <c r="B143" s="20"/>
-      <c r="C143" s="20"/>
-      <c r="D143" s="20"/>
-      <c r="E143" s="20"/>
-      <c r="F143" s="20"/>
-      <c r="G143" s="20"/>
-      <c r="H143" s="20"/>
-      <c r="I143" s="20"/>
-      <c r="J143" s="20"/>
-      <c r="K143" s="20"/>
+      <c r="A143" s="18"/>
+      <c r="B143" s="18"/>
+      <c r="C143" s="18"/>
+      <c r="D143" s="18"/>
+      <c r="E143" s="18"/>
+      <c r="F143" s="18"/>
+      <c r="G143" s="18"/>
+      <c r="H143" s="18"/>
+      <c r="I143" s="18"/>
+      <c r="J143" s="18"/>
+      <c r="K143" s="18"/>
     </row>
     <row r="144" spans="1:11">
-      <c r="A144" s="20"/>
-      <c r="B144" s="20"/>
-      <c r="C144" s="20"/>
-      <c r="D144" s="20"/>
-      <c r="E144" s="20"/>
-      <c r="F144" s="20"/>
-      <c r="G144" s="20"/>
-      <c r="H144" s="20"/>
-      <c r="I144" s="20"/>
-      <c r="J144" s="20"/>
-      <c r="K144" s="20"/>
+      <c r="A144" s="18"/>
+      <c r="B144" s="18"/>
+      <c r="C144" s="18"/>
+      <c r="D144" s="18"/>
+      <c r="E144" s="18"/>
+      <c r="F144" s="18"/>
+      <c r="G144" s="18"/>
+      <c r="H144" s="18"/>
+      <c r="I144" s="18"/>
+      <c r="J144" s="18"/>
+      <c r="K144" s="18"/>
     </row>
     <row r="145" spans="1:11">
-      <c r="A145" s="20"/>
-      <c r="B145" s="20"/>
-      <c r="C145" s="20"/>
-      <c r="D145" s="20"/>
-      <c r="E145" s="20"/>
-      <c r="F145" s="20"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="20"/>
-      <c r="I145" s="20"/>
-      <c r="J145" s="20"/>
-      <c r="K145" s="20"/>
+      <c r="A145" s="18"/>
+      <c r="B145" s="18"/>
+      <c r="C145" s="18"/>
+      <c r="D145" s="18"/>
+      <c r="E145" s="18"/>
+      <c r="F145" s="18"/>
+      <c r="G145" s="18"/>
+      <c r="H145" s="18"/>
+      <c r="I145" s="18"/>
+      <c r="J145" s="18"/>
+      <c r="K145" s="18"/>
     </row>
     <row r="146" spans="1:11">
-      <c r="A146" s="20"/>
-      <c r="B146" s="20"/>
-      <c r="C146" s="20"/>
-      <c r="D146" s="20"/>
-      <c r="E146" s="20"/>
-      <c r="F146" s="20"/>
-      <c r="G146" s="20"/>
-      <c r="H146" s="20"/>
-      <c r="I146" s="20"/>
-      <c r="J146" s="20"/>
-      <c r="K146" s="20"/>
+      <c r="A146" s="18"/>
+      <c r="B146" s="18"/>
+      <c r="C146" s="18"/>
+      <c r="D146" s="18"/>
+      <c r="E146" s="18"/>
+      <c r="F146" s="18"/>
+      <c r="G146" s="18"/>
+      <c r="H146" s="18"/>
+      <c r="I146" s="18"/>
+      <c r="J146" s="18"/>
+      <c r="K146" s="18"/>
     </row>
     <row r="147" spans="1:11">
-      <c r="A147" s="20"/>
-      <c r="B147" s="20"/>
-      <c r="C147" s="20"/>
-      <c r="D147" s="20"/>
-      <c r="E147" s="20"/>
-      <c r="F147" s="20"/>
-      <c r="G147" s="20"/>
-      <c r="H147" s="20"/>
-      <c r="I147" s="20"/>
-      <c r="J147" s="20"/>
-      <c r="K147" s="20"/>
+      <c r="A147" s="18"/>
+      <c r="B147" s="18"/>
+      <c r="C147" s="18"/>
+      <c r="D147" s="18"/>
+      <c r="E147" s="18"/>
+      <c r="F147" s="18"/>
+      <c r="G147" s="18"/>
+      <c r="H147" s="18"/>
+      <c r="I147" s="18"/>
+      <c r="J147" s="18"/>
+      <c r="K147" s="18"/>
     </row>
     <row r="148" spans="1:11">
-      <c r="A148" s="20"/>
-      <c r="B148" s="20"/>
-      <c r="C148" s="20"/>
-      <c r="D148" s="20"/>
-      <c r="E148" s="20"/>
-      <c r="F148" s="20"/>
-      <c r="G148" s="20"/>
-      <c r="H148" s="20"/>
-      <c r="I148" s="20"/>
-      <c r="J148" s="20"/>
-      <c r="K148" s="20"/>
+      <c r="A148" s="18"/>
+      <c r="B148" s="18"/>
+      <c r="C148" s="18"/>
+      <c r="D148" s="18"/>
+      <c r="E148" s="18"/>
+      <c r="F148" s="18"/>
+      <c r="G148" s="18"/>
+      <c r="H148" s="18"/>
+      <c r="I148" s="18"/>
+      <c r="J148" s="18"/>
+      <c r="K148" s="18"/>
     </row>
     <row r="149" spans="1:11">
-      <c r="A149" s="20"/>
-      <c r="B149" s="20"/>
-      <c r="C149" s="20"/>
-      <c r="D149" s="20"/>
-      <c r="E149" s="20"/>
-      <c r="F149" s="20"/>
-      <c r="G149" s="20"/>
-      <c r="H149" s="20"/>
-      <c r="I149" s="20"/>
-      <c r="J149" s="20"/>
-      <c r="K149" s="20"/>
+      <c r="A149" s="18"/>
+      <c r="B149" s="18"/>
+      <c r="C149" s="18"/>
+      <c r="D149" s="18"/>
+      <c r="E149" s="18"/>
+      <c r="F149" s="18"/>
+      <c r="G149" s="18"/>
+      <c r="H149" s="18"/>
+      <c r="I149" s="18"/>
+      <c r="J149" s="18"/>
+      <c r="K149" s="18"/>
     </row>
     <row r="150" spans="1:11">
-      <c r="A150" s="20"/>
-      <c r="B150" s="20"/>
-      <c r="C150" s="20"/>
-      <c r="D150" s="20"/>
-      <c r="E150" s="20"/>
-      <c r="F150" s="20"/>
-      <c r="G150" s="20"/>
-      <c r="H150" s="20"/>
-      <c r="I150" s="20"/>
-      <c r="J150" s="20"/>
-      <c r="K150" s="20"/>
+      <c r="A150" s="18"/>
+      <c r="B150" s="18"/>
+      <c r="C150" s="18"/>
+      <c r="D150" s="18"/>
+      <c r="E150" s="18"/>
+      <c r="F150" s="18"/>
+      <c r="G150" s="18"/>
+      <c r="H150" s="18"/>
+      <c r="I150" s="18"/>
+      <c r="J150" s="18"/>
+      <c r="K150" s="18"/>
     </row>
     <row r="151" spans="1:11">
-      <c r="A151" s="20"/>
-      <c r="B151" s="20"/>
-      <c r="C151" s="20"/>
-      <c r="D151" s="20"/>
-      <c r="E151" s="20"/>
-      <c r="F151" s="20"/>
-      <c r="G151" s="20"/>
-      <c r="H151" s="20"/>
-      <c r="I151" s="20"/>
-      <c r="J151" s="20"/>
-      <c r="K151" s="20"/>
+      <c r="A151" s="18"/>
+      <c r="B151" s="18"/>
+      <c r="C151" s="18"/>
+      <c r="D151" s="18"/>
+      <c r="E151" s="18"/>
+      <c r="F151" s="18"/>
+      <c r="G151" s="18"/>
+      <c r="H151" s="18"/>
+      <c r="I151" s="18"/>
+      <c r="J151" s="18"/>
+      <c r="K151" s="18"/>
     </row>
     <row r="152" spans="1:11">
-      <c r="A152" s="20"/>
-      <c r="B152" s="20"/>
-      <c r="C152" s="20"/>
-      <c r="D152" s="20"/>
-      <c r="E152" s="20"/>
-      <c r="F152" s="20"/>
-      <c r="G152" s="20"/>
-      <c r="H152" s="20"/>
-      <c r="I152" s="20"/>
-      <c r="J152" s="20"/>
-      <c r="K152" s="20"/>
+      <c r="A152" s="18"/>
+      <c r="B152" s="18"/>
+      <c r="C152" s="18"/>
+      <c r="D152" s="18"/>
+      <c r="E152" s="18"/>
+      <c r="F152" s="18"/>
+      <c r="G152" s="18"/>
+      <c r="H152" s="18"/>
+      <c r="I152" s="18"/>
+      <c r="J152" s="18"/>
+      <c r="K152" s="18"/>
     </row>
     <row r="153" spans="1:11">
-      <c r="A153" s="20"/>
-      <c r="B153" s="20"/>
-      <c r="C153" s="20"/>
-      <c r="D153" s="20"/>
-      <c r="E153" s="20"/>
-      <c r="F153" s="20"/>
-      <c r="G153" s="20"/>
-      <c r="H153" s="20"/>
-      <c r="I153" s="20"/>
-      <c r="J153" s="20"/>
-      <c r="K153" s="20"/>
+      <c r="A153" s="18"/>
+      <c r="B153" s="18"/>
+      <c r="C153" s="18"/>
+      <c r="D153" s="18"/>
+      <c r="E153" s="18"/>
+      <c r="F153" s="18"/>
+      <c r="G153" s="18"/>
+      <c r="H153" s="18"/>
+      <c r="I153" s="18"/>
+      <c r="J153" s="18"/>
+      <c r="K153" s="18"/>
     </row>
     <row r="154" spans="1:11">
-      <c r="A154" s="20"/>
-      <c r="B154" s="20"/>
-      <c r="C154" s="20"/>
-      <c r="D154" s="20"/>
-      <c r="E154" s="20"/>
-      <c r="F154" s="20"/>
-      <c r="G154" s="20"/>
-      <c r="H154" s="20"/>
-      <c r="I154" s="20"/>
-      <c r="J154" s="20"/>
-      <c r="K154" s="20"/>
+      <c r="A154" s="18"/>
+      <c r="B154" s="18"/>
+      <c r="C154" s="18"/>
+      <c r="D154" s="18"/>
+      <c r="E154" s="18"/>
+      <c r="F154" s="18"/>
+      <c r="G154" s="18"/>
+      <c r="H154" s="18"/>
+      <c r="I154" s="18"/>
+      <c r="J154" s="18"/>
+      <c r="K154" s="18"/>
     </row>
     <row r="155" spans="1:11">
-      <c r="A155" s="20"/>
-      <c r="B155" s="20"/>
-      <c r="C155" s="20"/>
-      <c r="D155" s="20"/>
-      <c r="E155" s="20"/>
-      <c r="F155" s="20"/>
-      <c r="G155" s="20"/>
-      <c r="H155" s="20"/>
-      <c r="I155" s="20"/>
-      <c r="J155" s="20"/>
-      <c r="K155" s="20"/>
+      <c r="A155" s="18"/>
+      <c r="B155" s="18"/>
+      <c r="C155" s="18"/>
+      <c r="D155" s="18"/>
+      <c r="E155" s="18"/>
+      <c r="F155" s="18"/>
+      <c r="G155" s="18"/>
+      <c r="H155" s="18"/>
+      <c r="I155" s="18"/>
+      <c r="J155" s="18"/>
+      <c r="K155" s="18"/>
     </row>
     <row r="156" spans="1:11">
-      <c r="A156" s="20"/>
-      <c r="B156" s="20"/>
-      <c r="C156" s="20"/>
-      <c r="D156" s="20"/>
-      <c r="E156" s="20"/>
-      <c r="F156" s="20"/>
-      <c r="G156" s="20"/>
-      <c r="H156" s="20"/>
-      <c r="I156" s="20"/>
-      <c r="J156" s="20"/>
-      <c r="K156" s="20"/>
+      <c r="A156" s="18"/>
+      <c r="B156" s="18"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="18"/>
+      <c r="E156" s="18"/>
+      <c r="F156" s="18"/>
+      <c r="G156" s="18"/>
+      <c r="H156" s="18"/>
+      <c r="I156" s="18"/>
+      <c r="J156" s="18"/>
+      <c r="K156" s="18"/>
     </row>
     <row r="157" spans="1:11">
-      <c r="A157" s="20"/>
-      <c r="B157" s="20"/>
-      <c r="C157" s="20"/>
-      <c r="D157" s="20"/>
-      <c r="E157" s="20"/>
-      <c r="F157" s="20"/>
-      <c r="G157" s="20"/>
-      <c r="H157" s="20"/>
-      <c r="I157" s="20"/>
-      <c r="J157" s="20"/>
-      <c r="K157" s="20"/>
+      <c r="A157" s="18"/>
+      <c r="B157" s="18"/>
+      <c r="C157" s="18"/>
+      <c r="D157" s="18"/>
+      <c r="E157" s="18"/>
+      <c r="F157" s="18"/>
+      <c r="G157" s="18"/>
+      <c r="H157" s="18"/>
+      <c r="I157" s="18"/>
+      <c r="J157" s="18"/>
+      <c r="K157" s="18"/>
     </row>
     <row r="158" spans="1:11">
-      <c r="A158" s="20"/>
-      <c r="B158" s="20"/>
-      <c r="C158" s="20"/>
-      <c r="D158" s="20"/>
-      <c r="E158" s="20"/>
-      <c r="F158" s="20"/>
-      <c r="G158" s="20"/>
-      <c r="H158" s="20"/>
-      <c r="I158" s="20"/>
-      <c r="J158" s="20"/>
-      <c r="K158" s="20"/>
+      <c r="A158" s="18"/>
+      <c r="B158" s="18"/>
+      <c r="C158" s="18"/>
+      <c r="D158" s="18"/>
+      <c r="E158" s="18"/>
+      <c r="F158" s="18"/>
+      <c r="G158" s="18"/>
+      <c r="H158" s="18"/>
+      <c r="I158" s="18"/>
+      <c r="J158" s="18"/>
+      <c r="K158" s="18"/>
     </row>
     <row r="159" spans="1:11">
-      <c r="A159" s="20"/>
-      <c r="B159" s="20"/>
-      <c r="C159" s="20"/>
-      <c r="D159" s="20"/>
-      <c r="E159" s="20"/>
-      <c r="F159" s="20"/>
-      <c r="G159" s="20"/>
-      <c r="H159" s="20"/>
-      <c r="I159" s="20"/>
-      <c r="J159" s="20"/>
-      <c r="K159" s="20"/>
+      <c r="A159" s="18"/>
+      <c r="B159" s="18"/>
+      <c r="C159" s="18"/>
+      <c r="D159" s="18"/>
+      <c r="E159" s="18"/>
+      <c r="F159" s="18"/>
+      <c r="G159" s="18"/>
+      <c r="H159" s="18"/>
+      <c r="I159" s="18"/>
+      <c r="J159" s="18"/>
+      <c r="K159" s="18"/>
     </row>
     <row r="160" spans="1:11">
-      <c r="A160" s="20"/>
-      <c r="B160" s="20"/>
-      <c r="C160" s="20"/>
-      <c r="D160" s="20"/>
-      <c r="E160" s="20"/>
-      <c r="F160" s="20"/>
-      <c r="G160" s="20"/>
-      <c r="H160" s="20"/>
-      <c r="I160" s="20"/>
-      <c r="J160" s="20"/>
-      <c r="K160" s="20"/>
+      <c r="A160" s="18"/>
+      <c r="B160" s="18"/>
+      <c r="C160" s="18"/>
+      <c r="D160" s="18"/>
+      <c r="E160" s="18"/>
+      <c r="F160" s="18"/>
+      <c r="G160" s="18"/>
+      <c r="H160" s="18"/>
+      <c r="I160" s="18"/>
+      <c r="J160" s="18"/>
+      <c r="K160" s="18"/>
     </row>
     <row r="161" spans="1:11">
-      <c r="A161" s="20"/>
-      <c r="B161" s="20"/>
-      <c r="C161" s="20"/>
-      <c r="D161" s="20"/>
-      <c r="E161" s="20"/>
-      <c r="F161" s="20"/>
-      <c r="G161" s="20"/>
-      <c r="H161" s="20"/>
-      <c r="I161" s="20"/>
-      <c r="J161" s="20"/>
-      <c r="K161" s="20"/>
+      <c r="A161" s="18"/>
+      <c r="B161" s="18"/>
+      <c r="C161" s="18"/>
+      <c r="D161" s="18"/>
+      <c r="E161" s="18"/>
+      <c r="F161" s="18"/>
+      <c r="G161" s="18"/>
+      <c r="H161" s="18"/>
+      <c r="I161" s="18"/>
+      <c r="J161" s="18"/>
+      <c r="K161" s="18"/>
     </row>
     <row r="162" spans="1:11">
-      <c r="A162" s="20"/>
-      <c r="B162" s="20"/>
-      <c r="C162" s="20"/>
-      <c r="D162" s="20"/>
-      <c r="E162" s="20"/>
-      <c r="F162" s="20"/>
-      <c r="G162" s="20"/>
-      <c r="H162" s="20"/>
-      <c r="I162" s="20"/>
-      <c r="J162" s="20"/>
-      <c r="K162" s="20"/>
+      <c r="A162" s="18"/>
+      <c r="B162" s="18"/>
+      <c r="C162" s="18"/>
+      <c r="D162" s="18"/>
+      <c r="E162" s="18"/>
+      <c r="F162" s="18"/>
+      <c r="G162" s="18"/>
+      <c r="H162" s="18"/>
+      <c r="I162" s="18"/>
+      <c r="J162" s="18"/>
+      <c r="K162" s="18"/>
     </row>
     <row r="163" spans="1:11">
-      <c r="A163" s="20"/>
-      <c r="B163" s="20"/>
-      <c r="C163" s="20"/>
-      <c r="D163" s="20"/>
-      <c r="E163" s="20"/>
-      <c r="F163" s="20"/>
-      <c r="G163" s="20"/>
-      <c r="H163" s="20"/>
-      <c r="I163" s="20"/>
-      <c r="J163" s="20"/>
-      <c r="K163" s="20"/>
+      <c r="A163" s="18"/>
+      <c r="B163" s="18"/>
+      <c r="C163" s="18"/>
+      <c r="D163" s="18"/>
+      <c r="E163" s="18"/>
+      <c r="F163" s="18"/>
+      <c r="G163" s="18"/>
+      <c r="H163" s="18"/>
+      <c r="I163" s="18"/>
+      <c r="J163" s="18"/>
+      <c r="K163" s="18"/>
     </row>
     <row r="164" spans="1:11">
-      <c r="A164" s="20"/>
-      <c r="B164" s="20"/>
-      <c r="C164" s="20"/>
-      <c r="D164" s="20"/>
-      <c r="E164" s="20"/>
-      <c r="F164" s="20"/>
-      <c r="G164" s="20"/>
-      <c r="H164" s="20"/>
-      <c r="I164" s="20"/>
-      <c r="J164" s="20"/>
-      <c r="K164" s="20"/>
+      <c r="A164" s="18"/>
+      <c r="B164" s="18"/>
+      <c r="C164" s="18"/>
+      <c r="D164" s="18"/>
+      <c r="E164" s="18"/>
+      <c r="F164" s="18"/>
+      <c r="G164" s="18"/>
+      <c r="H164" s="18"/>
+      <c r="I164" s="18"/>
+      <c r="J164" s="18"/>
+      <c r="K164" s="18"/>
     </row>
     <row r="165" spans="1:11">
-      <c r="A165" s="20"/>
-      <c r="B165" s="20"/>
-      <c r="C165" s="20"/>
-      <c r="D165" s="20"/>
-      <c r="E165" s="20"/>
-      <c r="F165" s="20"/>
-      <c r="G165" s="20"/>
-      <c r="H165" s="20"/>
-      <c r="I165" s="20"/>
-      <c r="J165" s="20"/>
-      <c r="K165" s="20"/>
+      <c r="A165" s="18"/>
+      <c r="B165" s="18"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="18"/>
+      <c r="E165" s="18"/>
+      <c r="F165" s="18"/>
+      <c r="G165" s="18"/>
+      <c r="H165" s="18"/>
+      <c r="I165" s="18"/>
+      <c r="J165" s="18"/>
+      <c r="K165" s="18"/>
     </row>
     <row r="166" spans="1:11">
-      <c r="A166" s="20"/>
-      <c r="B166" s="20"/>
-      <c r="C166" s="20"/>
-      <c r="D166" s="20"/>
-      <c r="E166" s="20"/>
-      <c r="F166" s="20"/>
-      <c r="G166" s="20"/>
-      <c r="H166" s="20"/>
-      <c r="I166" s="20"/>
-      <c r="J166" s="20"/>
-      <c r="K166" s="20"/>
+      <c r="A166" s="18"/>
+      <c r="B166" s="18"/>
+      <c r="C166" s="18"/>
+      <c r="D166" s="18"/>
+      <c r="E166" s="18"/>
+      <c r="F166" s="18"/>
+      <c r="G166" s="18"/>
+      <c r="H166" s="18"/>
+      <c r="I166" s="18"/>
+      <c r="J166" s="18"/>
+      <c r="K166" s="18"/>
     </row>
     <row r="167" spans="1:11">
-      <c r="A167" s="20"/>
-      <c r="B167" s="20"/>
-      <c r="C167" s="20"/>
-      <c r="D167" s="20"/>
-      <c r="E167" s="20"/>
-      <c r="F167" s="20"/>
-      <c r="G167" s="20"/>
-      <c r="H167" s="20"/>
-      <c r="I167" s="20"/>
-      <c r="J167" s="20"/>
-      <c r="K167" s="20"/>
+      <c r="A167" s="18"/>
+      <c r="B167" s="18"/>
+      <c r="C167" s="18"/>
+      <c r="D167" s="18"/>
+      <c r="E167" s="18"/>
+      <c r="F167" s="18"/>
+      <c r="G167" s="18"/>
+      <c r="H167" s="18"/>
+      <c r="I167" s="18"/>
+      <c r="J167" s="18"/>
+      <c r="K167" s="18"/>
     </row>
     <row r="168" spans="1:11">
-      <c r="A168" s="20"/>
-      <c r="B168" s="20"/>
-      <c r="C168" s="20"/>
-      <c r="D168" s="20"/>
-      <c r="E168" s="20"/>
-      <c r="F168" s="20"/>
-      <c r="G168" s="20"/>
-      <c r="H168" s="20"/>
-      <c r="I168" s="20"/>
-      <c r="J168" s="20"/>
-      <c r="K168" s="20"/>
+      <c r="A168" s="18"/>
+      <c r="B168" s="18"/>
+      <c r="C168" s="18"/>
+      <c r="D168" s="18"/>
+      <c r="E168" s="18"/>
+      <c r="F168" s="18"/>
+      <c r="G168" s="18"/>
+      <c r="H168" s="18"/>
+      <c r="I168" s="18"/>
+      <c r="J168" s="18"/>
+      <c r="K168" s="18"/>
     </row>
     <row r="169" spans="1:11">
-      <c r="A169" s="20"/>
-      <c r="B169" s="20"/>
-      <c r="C169" s="20"/>
-      <c r="D169" s="20"/>
-      <c r="E169" s="20"/>
-      <c r="F169" s="20"/>
-      <c r="G169" s="20"/>
-      <c r="H169" s="20"/>
-      <c r="I169" s="20"/>
-      <c r="J169" s="20"/>
-      <c r="K169" s="20"/>
+      <c r="A169" s="18"/>
+      <c r="B169" s="18"/>
+      <c r="C169" s="18"/>
+      <c r="D169" s="18"/>
+      <c r="E169" s="18"/>
+      <c r="F169" s="18"/>
+      <c r="G169" s="18"/>
+      <c r="H169" s="18"/>
+      <c r="I169" s="18"/>
+      <c r="J169" s="18"/>
+      <c r="K169" s="18"/>
     </row>
     <row r="170" spans="1:11">
-      <c r="A170" s="20"/>
-      <c r="B170" s="20"/>
-      <c r="C170" s="20"/>
-      <c r="D170" s="20"/>
-      <c r="E170" s="20"/>
-      <c r="F170" s="20"/>
-      <c r="G170" s="20"/>
-      <c r="H170" s="20"/>
-      <c r="I170" s="20"/>
-      <c r="J170" s="20"/>
-      <c r="K170" s="20"/>
+      <c r="A170" s="18"/>
+      <c r="B170" s="18"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="18"/>
+      <c r="E170" s="18"/>
+      <c r="F170" s="18"/>
+      <c r="G170" s="18"/>
+      <c r="H170" s="18"/>
+      <c r="I170" s="18"/>
+      <c r="J170" s="18"/>
+      <c r="K170" s="18"/>
     </row>
     <row r="171" spans="1:11">
-      <c r="A171" s="20"/>
-      <c r="B171" s="20"/>
-      <c r="C171" s="20"/>
-      <c r="D171" s="20"/>
-      <c r="E171" s="20"/>
-      <c r="F171" s="20"/>
-      <c r="G171" s="20"/>
-      <c r="H171" s="20"/>
-      <c r="I171" s="20"/>
-      <c r="J171" s="20"/>
-      <c r="K171" s="20"/>
+      <c r="A171" s="18"/>
+      <c r="B171" s="18"/>
+      <c r="C171" s="18"/>
+      <c r="D171" s="18"/>
+      <c r="E171" s="18"/>
+      <c r="F171" s="18"/>
+      <c r="G171" s="18"/>
+      <c r="H171" s="18"/>
+      <c r="I171" s="18"/>
+      <c r="J171" s="18"/>
+      <c r="K171" s="18"/>
     </row>
     <row r="172" spans="1:11">
-      <c r="A172" s="20"/>
-      <c r="B172" s="20"/>
-      <c r="C172" s="20"/>
-      <c r="D172" s="20"/>
-      <c r="E172" s="20"/>
-      <c r="F172" s="20"/>
-      <c r="G172" s="20"/>
-      <c r="H172" s="20"/>
-      <c r="I172" s="20"/>
-      <c r="J172" s="20"/>
-      <c r="K172" s="20"/>
+      <c r="A172" s="18"/>
+      <c r="B172" s="18"/>
+      <c r="C172" s="18"/>
+      <c r="D172" s="18"/>
+      <c r="E172" s="18"/>
+      <c r="F172" s="18"/>
+      <c r="G172" s="18"/>
+      <c r="H172" s="18"/>
+      <c r="I172" s="18"/>
+      <c r="J172" s="18"/>
+      <c r="K172" s="18"/>
     </row>
     <row r="173" spans="1:11">
-      <c r="A173" s="20"/>
-      <c r="B173" s="20"/>
-      <c r="C173" s="20"/>
-      <c r="D173" s="20"/>
-      <c r="E173" s="20"/>
-      <c r="F173" s="20"/>
-      <c r="G173" s="20"/>
-      <c r="H173" s="20"/>
-      <c r="I173" s="20"/>
-      <c r="J173" s="20"/>
-      <c r="K173" s="20"/>
+      <c r="A173" s="18"/>
+      <c r="B173" s="18"/>
+      <c r="C173" s="18"/>
+      <c r="D173" s="18"/>
+      <c r="E173" s="18"/>
+      <c r="F173" s="18"/>
+      <c r="G173" s="18"/>
+      <c r="H173" s="18"/>
+      <c r="I173" s="18"/>
+      <c r="J173" s="18"/>
+      <c r="K173" s="18"/>
     </row>
     <row r="174" spans="1:11">
-      <c r="A174" s="20"/>
-      <c r="B174" s="20"/>
-      <c r="C174" s="20"/>
-      <c r="D174" s="20"/>
-      <c r="E174" s="20"/>
-      <c r="F174" s="20"/>
-      <c r="G174" s="20"/>
-      <c r="H174" s="20"/>
-      <c r="I174" s="20"/>
-      <c r="J174" s="20"/>
-      <c r="K174" s="20"/>
+      <c r="A174" s="18"/>
+      <c r="B174" s="18"/>
+      <c r="C174" s="18"/>
+      <c r="D174" s="18"/>
+      <c r="E174" s="18"/>
+      <c r="F174" s="18"/>
+      <c r="G174" s="18"/>
+      <c r="H174" s="18"/>
+      <c r="I174" s="18"/>
+      <c r="J174" s="18"/>
+      <c r="K174" s="18"/>
     </row>
     <row r="175" spans="1:11">
-      <c r="A175" s="20"/>
-      <c r="B175" s="20"/>
-      <c r="C175" s="20"/>
-      <c r="D175" s="20"/>
-      <c r="E175" s="20"/>
-      <c r="F175" s="20"/>
-      <c r="G175" s="20"/>
-      <c r="H175" s="20"/>
-      <c r="I175" s="20"/>
-      <c r="J175" s="20"/>
-      <c r="K175" s="20"/>
+      <c r="A175" s="18"/>
+      <c r="B175" s="18"/>
+      <c r="C175" s="18"/>
+      <c r="D175" s="18"/>
+      <c r="E175" s="18"/>
+      <c r="F175" s="18"/>
+      <c r="G175" s="18"/>
+      <c r="H175" s="18"/>
+      <c r="I175" s="18"/>
+      <c r="J175" s="18"/>
+      <c r="K175" s="18"/>
     </row>
     <row r="176" spans="1:11">
-      <c r="A176" s="20"/>
-      <c r="B176" s="20"/>
-      <c r="C176" s="20"/>
-      <c r="D176" s="20"/>
-      <c r="E176" s="20"/>
-      <c r="F176" s="20"/>
-      <c r="G176" s="20"/>
-      <c r="H176" s="20"/>
-      <c r="I176" s="20"/>
-      <c r="J176" s="20"/>
-      <c r="K176" s="20"/>
+      <c r="A176" s="18"/>
+      <c r="B176" s="18"/>
+      <c r="C176" s="18"/>
+      <c r="D176" s="18"/>
+      <c r="E176" s="18"/>
+      <c r="F176" s="18"/>
+      <c r="G176" s="18"/>
+      <c r="H176" s="18"/>
+      <c r="I176" s="18"/>
+      <c r="J176" s="18"/>
+      <c r="K176" s="18"/>
     </row>
     <row r="177" spans="1:11">
-      <c r="A177" s="20"/>
-      <c r="B177" s="20"/>
-      <c r="C177" s="20"/>
-      <c r="D177" s="20"/>
-      <c r="E177" s="20"/>
-      <c r="F177" s="20"/>
-      <c r="G177" s="20"/>
-      <c r="H177" s="20"/>
-      <c r="I177" s="20"/>
-      <c r="J177" s="20"/>
-      <c r="K177" s="20"/>
+      <c r="A177" s="18"/>
+      <c r="B177" s="18"/>
+      <c r="C177" s="18"/>
+      <c r="D177" s="18"/>
+      <c r="E177" s="18"/>
+      <c r="F177" s="18"/>
+      <c r="G177" s="18"/>
+      <c r="H177" s="18"/>
+      <c r="I177" s="18"/>
+      <c r="J177" s="18"/>
+      <c r="K177" s="18"/>
     </row>
     <row r="178" spans="1:11">
-      <c r="A178" s="20"/>
-      <c r="B178" s="20"/>
-      <c r="C178" s="20"/>
-      <c r="D178" s="20"/>
-      <c r="E178" s="20"/>
-      <c r="F178" s="20"/>
-      <c r="G178" s="20"/>
-      <c r="H178" s="20"/>
-      <c r="I178" s="20"/>
-      <c r="J178" s="20"/>
-      <c r="K178" s="20"/>
+      <c r="A178" s="18"/>
+      <c r="B178" s="18"/>
+      <c r="C178" s="18"/>
+      <c r="D178" s="18"/>
+      <c r="E178" s="18"/>
+      <c r="F178" s="18"/>
+      <c r="G178" s="18"/>
+      <c r="H178" s="18"/>
+      <c r="I178" s="18"/>
+      <c r="J178" s="18"/>
+      <c r="K178" s="18"/>
     </row>
     <row r="179" spans="1:11">
-      <c r="A179" s="20"/>
-      <c r="B179" s="20"/>
-      <c r="C179" s="20"/>
-      <c r="D179" s="20"/>
-      <c r="E179" s="20"/>
-      <c r="F179" s="20"/>
-      <c r="G179" s="20"/>
-      <c r="H179" s="20"/>
-      <c r="I179" s="20"/>
-      <c r="J179" s="20"/>
-      <c r="K179" s="20"/>
+      <c r="A179" s="18"/>
+      <c r="B179" s="18"/>
+      <c r="C179" s="18"/>
+      <c r="D179" s="18"/>
+      <c r="E179" s="18"/>
+      <c r="F179" s="18"/>
+      <c r="G179" s="18"/>
+      <c r="H179" s="18"/>
+      <c r="I179" s="18"/>
+      <c r="J179" s="18"/>
+      <c r="K179" s="18"/>
     </row>
     <row r="180" spans="1:11">
-      <c r="A180" s="20"/>
-      <c r="B180" s="20"/>
-      <c r="C180" s="20"/>
-      <c r="D180" s="20"/>
-      <c r="E180" s="20"/>
-      <c r="F180" s="20"/>
-      <c r="G180" s="20"/>
-      <c r="H180" s="20"/>
-      <c r="I180" s="20"/>
-      <c r="J180" s="20"/>
-      <c r="K180" s="20"/>
+      <c r="A180" s="18"/>
+      <c r="B180" s="18"/>
+      <c r="C180" s="18"/>
+      <c r="D180" s="18"/>
+      <c r="E180" s="18"/>
+      <c r="F180" s="18"/>
+      <c r="G180" s="18"/>
+      <c r="H180" s="18"/>
+      <c r="I180" s="18"/>
+      <c r="J180" s="18"/>
+      <c r="K180" s="18"/>
     </row>
     <row r="181" spans="1:11">
-      <c r="A181" s="20"/>
-      <c r="B181" s="20"/>
-      <c r="C181" s="20"/>
-      <c r="D181" s="20"/>
-      <c r="E181" s="20"/>
-      <c r="F181" s="20"/>
-      <c r="G181" s="20"/>
-      <c r="H181" s="20"/>
-      <c r="I181" s="20"/>
-      <c r="J181" s="20"/>
-      <c r="K181" s="20"/>
+      <c r="A181" s="18"/>
+      <c r="B181" s="18"/>
+      <c r="C181" s="18"/>
+      <c r="D181" s="18"/>
+      <c r="E181" s="18"/>
+      <c r="F181" s="18"/>
+      <c r="G181" s="18"/>
+      <c r="H181" s="18"/>
+      <c r="I181" s="18"/>
+      <c r="J181" s="18"/>
+      <c r="K181" s="18"/>
     </row>
     <row r="182" spans="1:11">
-      <c r="A182" s="20"/>
-      <c r="B182" s="20"/>
-      <c r="C182" s="20"/>
-      <c r="D182" s="20"/>
-      <c r="E182" s="20"/>
-      <c r="F182" s="20"/>
-      <c r="G182" s="20"/>
-      <c r="H182" s="20"/>
-      <c r="I182" s="20"/>
-      <c r="J182" s="20"/>
-      <c r="K182" s="20"/>
+      <c r="A182" s="18"/>
+      <c r="B182" s="18"/>
+      <c r="C182" s="18"/>
+      <c r="D182" s="18"/>
+      <c r="E182" s="18"/>
+      <c r="F182" s="18"/>
+      <c r="G182" s="18"/>
+      <c r="H182" s="18"/>
+      <c r="I182" s="18"/>
+      <c r="J182" s="18"/>
+      <c r="K182" s="18"/>
     </row>
     <row r="183" spans="1:11">
-      <c r="A183" s="20"/>
-      <c r="B183" s="20"/>
-      <c r="C183" s="20"/>
-      <c r="D183" s="20"/>
-      <c r="E183" s="20"/>
-      <c r="F183" s="20"/>
-      <c r="G183" s="20"/>
-      <c r="H183" s="20"/>
-      <c r="I183" s="20"/>
-      <c r="J183" s="20"/>
-      <c r="K183" s="20"/>
+      <c r="A183" s="18"/>
+      <c r="B183" s="18"/>
+      <c r="C183" s="18"/>
+      <c r="D183" s="18"/>
+      <c r="E183" s="18"/>
+      <c r="F183" s="18"/>
+      <c r="G183" s="18"/>
+      <c r="H183" s="18"/>
+      <c r="I183" s="18"/>
+      <c r="J183" s="18"/>
+      <c r="K183" s="18"/>
     </row>
     <row r="184" spans="1:11">
-      <c r="A184" s="20"/>
-      <c r="B184" s="20"/>
-      <c r="C184" s="20"/>
-      <c r="D184" s="20"/>
-      <c r="E184" s="20"/>
-      <c r="F184" s="20"/>
-      <c r="G184" s="20"/>
-      <c r="H184" s="20"/>
-      <c r="I184" s="20"/>
-      <c r="J184" s="20"/>
-      <c r="K184" s="20"/>
+      <c r="A184" s="18"/>
+      <c r="B184" s="18"/>
+      <c r="C184" s="18"/>
+      <c r="D184" s="18"/>
+      <c r="E184" s="18"/>
+      <c r="F184" s="18"/>
+      <c r="G184" s="18"/>
+      <c r="H184" s="18"/>
+      <c r="I184" s="18"/>
+      <c r="J184" s="18"/>
+      <c r="K184" s="18"/>
     </row>
     <row r="185" spans="1:11">
-      <c r="A185" s="20"/>
-      <c r="B185" s="20"/>
-      <c r="C185" s="20"/>
-      <c r="D185" s="20"/>
-      <c r="E185" s="20"/>
-      <c r="F185" s="20"/>
-      <c r="G185" s="20"/>
-      <c r="H185" s="20"/>
-      <c r="I185" s="20"/>
-      <c r="J185" s="20"/>
-      <c r="K185" s="20"/>
+      <c r="A185" s="18"/>
+      <c r="B185" s="18"/>
+      <c r="C185" s="18"/>
+      <c r="D185" s="18"/>
+      <c r="E185" s="18"/>
+      <c r="F185" s="18"/>
+      <c r="G185" s="18"/>
+      <c r="H185" s="18"/>
+      <c r="I185" s="18"/>
+      <c r="J185" s="18"/>
+      <c r="K185" s="18"/>
     </row>
     <row r="186" spans="1:11">
-      <c r="A186" s="20"/>
-      <c r="B186" s="20"/>
-      <c r="C186" s="20"/>
-      <c r="D186" s="20"/>
-      <c r="E186" s="20"/>
-      <c r="F186" s="20"/>
-      <c r="G186" s="20"/>
-      <c r="H186" s="20"/>
-      <c r="I186" s="20"/>
-      <c r="J186" s="20"/>
-      <c r="K186" s="20"/>
+      <c r="A186" s="18"/>
+      <c r="B186" s="18"/>
+      <c r="C186" s="18"/>
+      <c r="D186" s="18"/>
+      <c r="E186" s="18"/>
+      <c r="F186" s="18"/>
+      <c r="G186" s="18"/>
+      <c r="H186" s="18"/>
+      <c r="I186" s="18"/>
+      <c r="J186" s="18"/>
+      <c r="K186" s="18"/>
     </row>
     <row r="187" spans="1:11">
-      <c r="A187" s="20"/>
-      <c r="B187" s="20"/>
-      <c r="C187" s="20"/>
-      <c r="D187" s="20"/>
-      <c r="E187" s="20"/>
-      <c r="F187" s="20"/>
-      <c r="G187" s="20"/>
-      <c r="H187" s="20"/>
-      <c r="I187" s="20"/>
-      <c r="J187" s="20"/>
-      <c r="K187" s="20"/>
+      <c r="A187" s="18"/>
+      <c r="B187" s="18"/>
+      <c r="C187" s="18"/>
+      <c r="D187" s="18"/>
+      <c r="E187" s="18"/>
+      <c r="F187" s="18"/>
+      <c r="G187" s="18"/>
+      <c r="H187" s="18"/>
+      <c r="I187" s="18"/>
+      <c r="J187" s="18"/>
+      <c r="K187" s="18"/>
     </row>
     <row r="188" spans="1:11">
-      <c r="A188" s="20"/>
-      <c r="B188" s="20"/>
-      <c r="C188" s="20"/>
-      <c r="D188" s="20"/>
-      <c r="E188" s="20"/>
-      <c r="F188" s="20"/>
-      <c r="G188" s="20"/>
-      <c r="H188" s="20"/>
-      <c r="I188" s="20"/>
-      <c r="J188" s="20"/>
-      <c r="K188" s="20"/>
+      <c r="A188" s="18"/>
+      <c r="B188" s="18"/>
+      <c r="C188" s="18"/>
+      <c r="D188" s="18"/>
+      <c r="E188" s="18"/>
+      <c r="F188" s="18"/>
+      <c r="G188" s="18"/>
+      <c r="H188" s="18"/>
+      <c r="I188" s="18"/>
+      <c r="J188" s="18"/>
+      <c r="K188" s="18"/>
     </row>
     <row r="189" spans="1:11">
-      <c r="A189" s="20"/>
-      <c r="B189" s="20"/>
-      <c r="C189" s="20"/>
-      <c r="D189" s="20"/>
-      <c r="E189" s="20"/>
-      <c r="F189" s="20"/>
-      <c r="G189" s="20"/>
-      <c r="H189" s="20"/>
-      <c r="I189" s="20"/>
-      <c r="J189" s="20"/>
-      <c r="K189" s="20"/>
+      <c r="A189" s="18"/>
+      <c r="B189" s="18"/>
+      <c r="C189" s="18"/>
+      <c r="D189" s="18"/>
+      <c r="E189" s="18"/>
+      <c r="F189" s="18"/>
+      <c r="G189" s="18"/>
+      <c r="H189" s="18"/>
+      <c r="I189" s="18"/>
+      <c r="J189" s="18"/>
+      <c r="K189" s="18"/>
     </row>
     <row r="190" spans="1:11">
-      <c r="A190" s="20"/>
-      <c r="B190" s="20"/>
-      <c r="C190" s="20"/>
-      <c r="D190" s="20"/>
-      <c r="E190" s="20"/>
-      <c r="F190" s="20"/>
-      <c r="G190" s="20"/>
-      <c r="H190" s="20"/>
-      <c r="I190" s="20"/>
-      <c r="J190" s="20"/>
-      <c r="K190" s="20"/>
+      <c r="A190" s="18"/>
+      <c r="B190" s="18"/>
+      <c r="C190" s="18"/>
+      <c r="D190" s="18"/>
+      <c r="E190" s="18"/>
+      <c r="F190" s="18"/>
+      <c r="G190" s="18"/>
+      <c r="H190" s="18"/>
+      <c r="I190" s="18"/>
+      <c r="J190" s="18"/>
+      <c r="K190" s="18"/>
     </row>
     <row r="191" spans="1:11">
-      <c r="A191" s="20"/>
-      <c r="B191" s="20"/>
-      <c r="C191" s="20"/>
-      <c r="D191" s="20"/>
-      <c r="E191" s="20"/>
-      <c r="F191" s="20"/>
-      <c r="G191" s="20"/>
-      <c r="H191" s="20"/>
-      <c r="I191" s="20"/>
-      <c r="J191" s="20"/>
-      <c r="K191" s="20"/>
+      <c r="A191" s="18"/>
+      <c r="B191" s="18"/>
+      <c r="C191" s="18"/>
+      <c r="D191" s="18"/>
+      <c r="E191" s="18"/>
+      <c r="F191" s="18"/>
+      <c r="G191" s="18"/>
+      <c r="H191" s="18"/>
+      <c r="I191" s="18"/>
+      <c r="J191" s="18"/>
+      <c r="K191" s="18"/>
     </row>
     <row r="192" spans="1:11">
-      <c r="A192" s="20"/>
-      <c r="B192" s="20"/>
-      <c r="C192" s="20"/>
-      <c r="D192" s="20"/>
-      <c r="E192" s="20"/>
-      <c r="F192" s="20"/>
-      <c r="G192" s="20"/>
-      <c r="H192" s="20"/>
-      <c r="I192" s="20"/>
-      <c r="J192" s="20"/>
-      <c r="K192" s="20"/>
+      <c r="A192" s="18"/>
+      <c r="B192" s="18"/>
+      <c r="C192" s="18"/>
+      <c r="D192" s="18"/>
+      <c r="E192" s="18"/>
+      <c r="F192" s="18"/>
+      <c r="G192" s="18"/>
+      <c r="H192" s="18"/>
+      <c r="I192" s="18"/>
+      <c r="J192" s="18"/>
+      <c r="K192" s="18"/>
     </row>
     <row r="193" spans="1:11">
-      <c r="A193" s="20"/>
-      <c r="B193" s="20"/>
-      <c r="C193" s="20"/>
-      <c r="D193" s="20"/>
-      <c r="E193" s="20"/>
-      <c r="F193" s="20"/>
-      <c r="G193" s="20"/>
-      <c r="H193" s="20"/>
-      <c r="I193" s="20"/>
-      <c r="J193" s="20"/>
-      <c r="K193" s="20"/>
+      <c r="A193" s="18"/>
+      <c r="B193" s="18"/>
+      <c r="C193" s="18"/>
+      <c r="D193" s="18"/>
+      <c r="E193" s="18"/>
+      <c r="F193" s="18"/>
+      <c r="G193" s="18"/>
+      <c r="H193" s="18"/>
+      <c r="I193" s="18"/>
+      <c r="J193" s="18"/>
+      <c r="K193" s="18"/>
     </row>
     <row r="194" spans="1:11">
-      <c r="A194" s="20"/>
-      <c r="B194" s="20"/>
-      <c r="C194" s="20"/>
-      <c r="D194" s="20"/>
-      <c r="E194" s="20"/>
-      <c r="F194" s="20"/>
-      <c r="G194" s="20"/>
-      <c r="H194" s="20"/>
-      <c r="I194" s="20"/>
-      <c r="J194" s="20"/>
-      <c r="K194" s="20"/>
+      <c r="A194" s="18"/>
+      <c r="B194" s="18"/>
+      <c r="C194" s="18"/>
+      <c r="D194" s="18"/>
+      <c r="E194" s="18"/>
+      <c r="F194" s="18"/>
+      <c r="G194" s="18"/>
+      <c r="H194" s="18"/>
+      <c r="I194" s="18"/>
+      <c r="J194" s="18"/>
+      <c r="K194" s="18"/>
     </row>
     <row r="195" spans="1:11">
-      <c r="A195" s="20"/>
-      <c r="B195" s="20"/>
-      <c r="C195" s="20"/>
-      <c r="D195" s="20"/>
-      <c r="E195" s="20"/>
-      <c r="F195" s="20"/>
-      <c r="G195" s="20"/>
-      <c r="H195" s="20"/>
-      <c r="I195" s="20"/>
-      <c r="J195" s="20"/>
-      <c r="K195" s="20"/>
+      <c r="A195" s="18"/>
+      <c r="B195" s="18"/>
+      <c r="C195" s="18"/>
+      <c r="D195" s="18"/>
+      <c r="E195" s="18"/>
+      <c r="F195" s="18"/>
+      <c r="G195" s="18"/>
+      <c r="H195" s="18"/>
+      <c r="I195" s="18"/>
+      <c r="J195" s="18"/>
+      <c r="K195" s="18"/>
     </row>
     <row r="196" spans="1:11">
-      <c r="A196" s="20"/>
-      <c r="B196" s="20"/>
-      <c r="C196" s="20"/>
-      <c r="D196" s="20"/>
-      <c r="E196" s="20"/>
-      <c r="F196" s="20"/>
-      <c r="G196" s="20"/>
-      <c r="H196" s="20"/>
-      <c r="I196" s="20"/>
-      <c r="J196" s="20"/>
-      <c r="K196" s="20"/>
+      <c r="A196" s="18"/>
+      <c r="B196" s="18"/>
+      <c r="C196" s="18"/>
+      <c r="D196" s="18"/>
+      <c r="E196" s="18"/>
+      <c r="F196" s="18"/>
+      <c r="G196" s="18"/>
+      <c r="H196" s="18"/>
+      <c r="I196" s="18"/>
+      <c r="J196" s="18"/>
+      <c r="K196" s="18"/>
     </row>
     <row r="197" spans="1:11">
-      <c r="A197" s="20"/>
-      <c r="B197" s="20"/>
-      <c r="C197" s="20"/>
-      <c r="D197" s="20"/>
-      <c r="E197" s="20"/>
-      <c r="F197" s="20"/>
-      <c r="G197" s="20"/>
-      <c r="H197" s="20"/>
-      <c r="I197" s="20"/>
-      <c r="J197" s="20"/>
-      <c r="K197" s="20"/>
+      <c r="A197" s="18"/>
+      <c r="B197" s="18"/>
+      <c r="C197" s="18"/>
+      <c r="D197" s="18"/>
+      <c r="E197" s="18"/>
+      <c r="F197" s="18"/>
+      <c r="G197" s="18"/>
+      <c r="H197" s="18"/>
+      <c r="I197" s="18"/>
+      <c r="J197" s="18"/>
+      <c r="K197" s="18"/>
     </row>
     <row r="198" spans="1:11">
-      <c r="A198" s="20"/>
-      <c r="B198" s="20"/>
-      <c r="C198" s="20"/>
-      <c r="D198" s="20"/>
-      <c r="E198" s="20"/>
-      <c r="F198" s="20"/>
-      <c r="G198" s="20"/>
-      <c r="H198" s="20"/>
-      <c r="I198" s="20"/>
-      <c r="J198" s="20"/>
-      <c r="K198" s="20"/>
+      <c r="A198" s="18"/>
+      <c r="B198" s="18"/>
+      <c r="C198" s="18"/>
+      <c r="D198" s="18"/>
+      <c r="E198" s="18"/>
+      <c r="F198" s="18"/>
+      <c r="G198" s="18"/>
+      <c r="H198" s="18"/>
+      <c r="I198" s="18"/>
+      <c r="J198" s="18"/>
+      <c r="K198" s="18"/>
     </row>
     <row r="199" spans="1:11">
-      <c r="A199" s="20"/>
-      <c r="B199" s="20"/>
-      <c r="C199" s="20"/>
-      <c r="D199" s="20"/>
-      <c r="E199" s="20"/>
-      <c r="F199" s="20"/>
-      <c r="G199" s="20"/>
-      <c r="H199" s="20"/>
-      <c r="I199" s="20"/>
-      <c r="J199" s="20"/>
-      <c r="K199" s="20"/>
+      <c r="A199" s="18"/>
+      <c r="B199" s="18"/>
+      <c r="C199" s="18"/>
+      <c r="D199" s="18"/>
+      <c r="E199" s="18"/>
+      <c r="F199" s="18"/>
+      <c r="G199" s="18"/>
+      <c r="H199" s="18"/>
+      <c r="I199" s="18"/>
+      <c r="J199" s="18"/>
+      <c r="K199" s="18"/>
     </row>
     <row r="200" spans="1:11">
-      <c r="A200" s="20"/>
-      <c r="B200" s="20"/>
-      <c r="C200" s="20"/>
-      <c r="D200" s="20"/>
-      <c r="E200" s="20"/>
-      <c r="F200" s="20"/>
-      <c r="G200" s="20"/>
-      <c r="H200" s="20"/>
-      <c r="I200" s="20"/>
-      <c r="J200" s="20"/>
-      <c r="K200" s="20"/>
+      <c r="A200" s="18"/>
+      <c r="B200" s="18"/>
+      <c r="C200" s="18"/>
+      <c r="D200" s="18"/>
+      <c r="E200" s="18"/>
+      <c r="F200" s="18"/>
+      <c r="G200" s="18"/>
+      <c r="H200" s="18"/>
+      <c r="I200" s="18"/>
+      <c r="J200" s="18"/>
+      <c r="K200" s="18"/>
     </row>
     <row r="201" spans="1:11">
-      <c r="A201" s="20"/>
-      <c r="B201" s="20"/>
-      <c r="C201" s="20"/>
-      <c r="D201" s="20"/>
-      <c r="E201" s="20"/>
-      <c r="F201" s="20"/>
-      <c r="G201" s="20"/>
-      <c r="H201" s="20"/>
-      <c r="I201" s="20"/>
-      <c r="J201" s="20"/>
-      <c r="K201" s="20"/>
+      <c r="A201" s="18"/>
+      <c r="B201" s="18"/>
+      <c r="C201" s="18"/>
+      <c r="D201" s="18"/>
+      <c r="E201" s="18"/>
+      <c r="F201" s="18"/>
+      <c r="G201" s="18"/>
+      <c r="H201" s="18"/>
+      <c r="I201" s="18"/>
+      <c r="J201" s="18"/>
+      <c r="K201" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" sqref="A2:A501" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
@@ -4233,17 +4277,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -4254,17 +4298,17 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -4275,17 +4319,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>122</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>123</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -4296,17 +4340,17 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>125</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -4317,17 +4361,17 @@
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>127</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>128</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -4338,17 +4382,17 @@
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>130</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -4359,17 +4403,17 @@
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>131</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>132</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -4380,17 +4424,17 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>135</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -4401,17 +4445,17 @@
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>137</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -4422,17 +4466,17 @@
         <v>1</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>138</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>139</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -4443,17 +4487,17 @@
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>140</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>141</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -4464,17 +4508,17 @@
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>142</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>143</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -4485,17 +4529,17 @@
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>144</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>145</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -4506,17 +4550,17 @@
         <v>1</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -4527,17 +4571,17 @@
         <v>1</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -4548,17 +4592,17 @@
         <v>1</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>151</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>152</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -4569,17 +4613,17 @@
         <v>1</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -4590,17 +4634,17 @@
         <v>1</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>155</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>156</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -4611,17 +4655,17 @@
         <v>1</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>158</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>159</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -4632,17 +4676,17 @@
         <v>1</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>161</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -4653,17 +4697,17 @@
         <v>1</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>162</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>163</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -4674,17 +4718,17 @@
         <v>1</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>166</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -4695,17 +4739,17 @@
         <v>1</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>167</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>168</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -4716,17 +4760,17 @@
         <v>1</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>170</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>171</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -4737,17 +4781,17 @@
         <v>1</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>172</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>173</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -4758,17 +4802,17 @@
         <v>1</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>175</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>176</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -4779,17 +4823,17 @@
         <v>1</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>177</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>178</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -4800,17 +4844,17 @@
         <v>1</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
@@ -4821,17 +4865,17 @@
         <v>1</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -4842,17 +4886,17 @@
         <v>1</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
@@ -4863,17 +4907,17 @@
         <v>1</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -4884,17 +4928,17 @@
         <v>1</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -4905,17 +4949,17 @@
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -4926,17 +4970,17 @@
         <v>1</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -4947,17 +4991,17 @@
         <v>1</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -4968,17 +5012,17 @@
         <v>1</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -4989,17 +5033,17 @@
         <v>1</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -5010,17 +5054,17 @@
         <v>1</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -5031,17 +5075,17 @@
         <v>1</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -5052,17 +5096,17 @@
         <v>1</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -5073,17 +5117,17 @@
         <v>1</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -5094,17 +5138,17 @@
         <v>1</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -5115,17 +5159,17 @@
         <v>1</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -5136,17 +5180,17 @@
         <v>1</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -5157,17 +5201,17 @@
         <v>1</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -5178,17 +5222,17 @@
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -5199,17 +5243,17 @@
         <v>1</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
@@ -5220,17 +5264,17 @@
         <v>1</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
@@ -5241,17 +5285,17 @@
         <v>1</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -5262,17 +5306,17 @@
         <v>1</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
@@ -5283,17 +5327,17 @@
         <v>1</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
@@ -5304,17 +5348,17 @@
         <v>1</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
@@ -5325,17 +5369,17 @@
         <v>1</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
@@ -5346,17 +5390,17 @@
         <v>1</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -5367,17 +5411,17 @@
         <v>1</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -5388,17 +5432,17 @@
         <v>1</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -16526,20 +16570,20 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="64" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Desktop/연구실 홈페이지/lab-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D92088-558D-444E-BD12-48ABB6F55B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FCE936-DBB3-794C-B08F-6BB3256AFB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="740" yWindow="1880" windowWidth="38580" windowHeight="24980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -698,19 +698,7 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>숭실대학교 IT대학 글로벌미디어학부 공학사
-숭실대학교 사회과학대학 평생교육학과 문학사(복수전공)
-숭실대학교 일반대학원 평생교육학과 교육학석사</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>researcher</t>
-  </si>
-  <si>
-    <t>숭실대학교 인문대학 기독교학과 문학사
-FH Vorarlberg (Austria) Exchange Student
-숭실대학교 일반대학원 평생교육학과 교육학석사</t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>jane6920@naver.com</t>
@@ -737,25 +725,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>Wuhan Huaxia University of Technology 영어학과 학사 졸업
-The Education University of Hong Kong 교육학과 석사 졸업
-숭실대학교 일반대학원 평생교육학과 박사 수료</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>세종대학교 공공정책대학원 사회복지학과 석사 졸업
-숭실대학교 일반대학원 평생교육학과 박사 수료</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국대학교육협의회 (2026.09 ~ 재직중)
-외국인 유학생 학습경험 및 대학적응 연구 프로젝트 수행 중
-국제개발협력(ODA) 교육과정 개발 및 수요 분석 프로젝트 참여
-김예빈, 기영화. (2026). 한국 체류 유럽권 교환학생의 전환학습 경험에 관한 내러티브 탐구. 문화교류와 다문화교육, 15(1), 227–251.
-김예빈. (2025). 고등교육기관 단기 교환학생의 전환적 여정에 관한 내러티브 탐구 [석사학위논문, 숭실대학교].</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>alumni_ma1</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -844,26 +813,57 @@
     <t>alumni_ma29</t>
   </si>
   <si>
-    <t>(주)멀티캠퍼스 삼성청년SW·AI아카데미 교육운영 (2025.02 ~ 재직중)
-(주)데이원컴퍼니 패스트캠퍼스CIC 집체교육사업 Project Manager (2024.07 ~ 2025.01)
-K-시그니처 협력사업 (혁신적 농촌공동체 개발 프로그램 세네갈 연수원 운영과 커리큘럼 개발) 연구지원인력 (2025.03 ~ 2025.06)
-새마을재단 르완다 협동조합 역량강화사업 종료평가와 코트디부아르 시범마을 조성사업 사후평가 참여 (2024.03 ~ 2024.11)
-숭실대학교 교수학습센터 경험학습 최적화를 위한 META 교육학습체계 구축 교과목 개발 참여자 (2023.03 ~ 2024.01)
-기영화, 신지훈. (2026). 새마을 ODA 사업의 농촌연수원 설립 관련 이해관계자 담론구조와 운영에 관한 텍스트 의미연결망 분석: 세네갈 남부 K지역 사례를 중심으로. 사회적경제와 정책연구, 16(3), 73-101.
-신지훈. (2026). 평생교육진흥기본계획과 정책연구 간 직업교육 의제 정합성 분석 [석사학위논문, 숭실대학교].</t>
+    <t>• (주)멀티캠퍼스 삼성청년SW·AI아카데미 교육운영 (2025.02 ~ 재직중)
+• (주)데이원컴퍼니 패스트캠퍼스CIC 집체교육사업 Project Manager (2024.07 ~ 2025.01)
+• K-시그니처 협력사업 (혁신적 농촌공동체 개발 프로그램 세네갈 연수원 운영과 커리큘럼 개발) 연구지원인력 (2025.03 ~ 2025.06)
+• 새마을재단 르완다 새마을 협동조합 역량강화사업 종료평가·코트디부아르 새마을 시범마을 조성사업 사후평가 참여 (2024.03 ~ 2024.11)
+• 숭실대학교 교수학습센터 경험학습 최적화를 위한 META 교육학습체계 구축 교과목 개발 참여자 (2023.03 ~ 2024.01)
+• 기영화, 신지훈. (2026). 새마을 ODA 사업의 농촌연수원 설립 관련 이해관계자 담론구조와 운영에 관한 텍스트 의미연결망 분석: 세네갈 남부 K지역 사례를 중심으로. 사회적경제와 정책연구, 16(3), 73-101.
+• 신지훈. (2026). 평생교육진흥기본계획과 정책연구 간 직업교육 의제 정합성 분석 [석사학위논문, 숭실대학교].</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>숭실대학교 국제처 유학생 지원 및 관리 (2025.03 ~ 2026.08)
-평생교육 및 성인교육 관련 연구 수행 (2024 ~ 현재)
-외국인 유학생의 대학생활적응 및 고등교육 관련 연구 수행 (2025 ~ 현재)
-양사동, 기영화. (2026). 외국인 유학생 문화적응 과정 탐색. 한국과 세계, 8(1), 277-310.</t>
+    <t>• 숭실대학교 IT대학 글로벌미디어학부 공학사
+• 숭실대학교 사회과학대학 평생교육학과 문학사(복수전공)
+• 숭실대학교 일반대학원 평생교육학과 교육학석사</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>한국창의 인성교육센터 구군인성교육 강의
-박시언, 기영화. (2026). 행동 사건 면담 (BEI)을 활용한 노인주간보호센터 사회복지사의 역량 모델 개발. 한국케어매니지먼트 연구, 59, 117-152.
-박시언, 기영화. (2025). 군 인성교육 외부 강사의 전문성 형성 과정에 관한 근거이론 연구. 인성교육연구, 10(2), 27-61.</t>
+    <t>• 세종대학교 공공정책대학원 사회복지학과 석사 졸업
+• 숭실대학교 일반대학원 평생교육학과 박사 수료</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>• Wuhan Huaxia University of Technology 영어학과 학사 졸업
+• The Education University of Hong Kong 교육학과 석사 졸업
+• 숭실대학교 일반대학원 평생교육학과 박사 수료</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>• 숭실대학교 인문대학 기독교학과 문학사
+• FH Vorarlberg (Austria) Exchange Student
+• 숭실대학교 일반대학원 평생교육학과 교육학석사</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>• 한국창의 인성교육센터 구군인성교육 강의
+• 박시언, 기영화. (2026). 행동 사건 면담 (BEI)을 활용한 노인주간보호센터 사회복지사의 역량 모델 개발. 한국케어매니지먼트 연구, 59, 117-152.
+• 박시언, 기영화. (2025). 군 인성교육 외부 강사의 전문성 형성 과정에 관한 근거이론 연구. 인성교육연구, 10(2), 27-61.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>• 숭실대학교 국제처 유학생 지원 및 관리 (2025.03 ~ 2026.08)
+• 평생교육 및 성인교육 관련 연구 수행 (2024 ~ 현재)
+• 외국인 유학생의 대학생활적응 및 고등교육 관련 연구 수행 (2025 ~ 현재)
+• 양사동, 기영화. (2026). 외국인 유학생 문화적응 과정 탐색. 한국과 세계, 8(1), 277-310.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>• 한국대학교육협의회 (2026.09 ~ 재직중)
+• 외국인 유학생 학습경험 및 대학적응 연구 프로젝트 수행 중
+• 국제개발협력(ODA) 교육과정 개발 및 수요 분석 프로젝트 참여
+• 김예빈, 기영화. (2026). 한국 체류 유럽권 교환학생의 전환학습 경험에 관한 내러티브 탐구. 문화교류와 다문화교육, 15(1), 227–251.
+• 김예빈. (2025). 고등교육기관 단기 교환학생의 전환적 여정에 관한 내러티브 탐구 [석사학위논문, 숭실대학교].</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1514,7 +1514,7 @@
         <v>37</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>102</v>
@@ -1526,10 +1526,10 @@
         <v>104</v>
       </c>
       <c r="L3" s="17" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="M3" s="17" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="90">
@@ -1559,10 +1559,10 @@
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
       <c r="L4" s="17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="90">
@@ -1588,10 +1588,10 @@
         <v>108</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18" t="s">
@@ -1601,7 +1601,7 @@
         <v>254</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="120">
@@ -1621,26 +1621,26 @@
         <v>114</v>
       </c>
       <c r="F6" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>213</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>215</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18" t="s">
         <v>115</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -4180,7 +4180,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" sqref="A2:A501" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
@@ -4844,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C30" s="12" t="s">
         <v>178</v>
@@ -4865,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>180</v>
@@ -4886,7 +4886,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>181</v>
@@ -4907,7 +4907,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>182</v>
@@ -4928,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>183</v>
@@ -4949,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>184</v>
@@ -4970,7 +4970,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>186</v>
@@ -4991,7 +4991,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>187</v>
@@ -5012,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>188</v>
@@ -5033,7 +5033,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>189</v>
@@ -5054,7 +5054,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>190</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>191</v>
@@ -5096,7 +5096,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>192</v>
@@ -5117,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>193</v>
@@ -5138,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>194</v>
@@ -5159,7 +5159,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>195</v>
@@ -5180,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>170</v>
@@ -5201,7 +5201,7 @@
         <v>1</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>196</v>
@@ -5222,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>172</v>
@@ -5243,7 +5243,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>197</v>
@@ -5264,7 +5264,7 @@
         <v>1</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>198</v>
@@ -5285,7 +5285,7 @@
         <v>1</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>199</v>
@@ -5306,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>200</v>
@@ -5327,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>201</v>
@@ -5348,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>202</v>
@@ -5369,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>203</v>
@@ -5390,7 +5390,7 @@
         <v>1</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>204</v>
@@ -5411,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>206</v>
@@ -5432,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>208</v>

--- a/data/kee_lab_content.xlsx
+++ b/data/kee_lab_content.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jihoon/Desktop/연구실 홈페이지/lab-main/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E938ED3-5A4A-D941-81EF-6C04E47D47DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9633DB8-512D-1940-9E25-9B34EB68EDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="740" yWindow="1860" windowWidth="38580" windowHeight="24980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="740" yWindow="1860" windowWidth="38580" windowHeight="24980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -383,10 +383,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>YANG SIDONG</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>yangsidong.jpeg</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -2959,6 +2955,10 @@
   </si>
   <si>
     <t>학점은행제 운영방안연구</t>
+  </si>
+  <si>
+    <t>YANG SITONG</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3546,10 +3546,10 @@
         <v>32</v>
       </c>
       <c r="L1" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="M1" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16">
@@ -3608,7 +3608,7 @@
         <v>37</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>102</v>
@@ -3620,10 +3620,10 @@
         <v>104</v>
       </c>
       <c r="L3" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="M3" s="17" t="s">
         <v>248</v>
-      </c>
-      <c r="M3" s="17" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="90">
@@ -3653,10 +3653,10 @@
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
       <c r="L4" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="90">
@@ -3673,7 +3673,7 @@
         <v>109</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>110</v>
+        <v>953</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>36</v>
@@ -3682,20 +3682,20 @@
         <v>108</v>
       </c>
       <c r="H5" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="I5" s="19" t="s">
         <v>215</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>216</v>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="120">
@@ -3703,38 +3703,38 @@
         <v>1</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="18">
         <v>4</v>
       </c>
       <c r="D6" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>114</v>
-      </c>
       <c r="F6" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" s="19" t="s">
         <v>212</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="I6" s="19" t="s">
-        <v>213</v>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -6371,17 +6371,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>116</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>117</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -6392,17 +6392,17 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>120</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -6413,17 +6413,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -6434,17 +6434,17 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>123</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>124</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -6455,17 +6455,17 @@
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>127</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -6476,17 +6476,17 @@
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>128</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>129</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -6497,17 +6497,17 @@
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>130</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>131</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -6518,17 +6518,17 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -6539,17 +6539,17 @@
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>135</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>136</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -6560,17 +6560,17 @@
         <v>1</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>137</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>138</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -6581,17 +6581,17 @@
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>140</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -6602,17 +6602,17 @@
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>142</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -6623,17 +6623,17 @@
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>144</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -6644,17 +6644,17 @@
         <v>1</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>145</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>146</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -6665,17 +6665,17 @@
         <v>1</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>148</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>149</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -6686,17 +6686,17 @@
         <v>1</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>150</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>151</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -6707,17 +6707,17 @@
         <v>1</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>152</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -6728,17 +6728,17 @@
         <v>1</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>154</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -6749,17 +6749,17 @@
         <v>1</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -6770,17 +6770,17 @@
         <v>1</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>159</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>160</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -6791,17 +6791,17 @@
         <v>1</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>161</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>162</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -6812,17 +6812,17 @@
         <v>1</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>164</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>165</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -6833,17 +6833,17 @@
         <v>1</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>166</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>167</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -6854,17 +6854,17 @@
         <v>1</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -6875,17 +6875,17 @@
         <v>1</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C27" s="12" t="s">
         <v>171</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>172</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -6896,17 +6896,17 @@
         <v>1</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>174</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>175</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -6917,17 +6917,17 @@
         <v>1</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>176</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>177</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -6938,17 +6938,17 @@
         <v>1</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
@@ -6959,17 +6959,17 @@
         <v>1</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -6980,17 +6980,17 @@
         <v>1</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
@@ -7001,17 +7001,17 @@
         <v>1</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -7022,17 +7022,17 @@
         <v>1</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -7043,17 +7043,17 @@
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -7064,17 +7064,17 @@
         <v>1</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -7085,17 +7085,17 @@
         <v>1</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -7106,17 +7106,17 @@
         <v>1</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -7127,17 +7127,17 @@
         <v>1</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -7148,17 +7148,17 @@
         <v>1</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -7169,17 +7169,17 @@
         <v>1</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -7190,17 +7190,17 @@
         <v>1</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -7211,17 +7211,17 @@
         <v>1</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -7232,17 +7232,17 @@
         <v>1</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -7253,17 +7253,17 @@
         <v>1</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -7274,17 +7274,17 @@
         <v>1</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -7295,17 +7295,17 @@
         <v>1</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -7316,17 +7316,17 @@
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -7337,17 +7337,17 @@
         <v>1</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
@@ -7358,17 +7358,17 @@
         <v>1</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
@@ -7379,17 +7379,17 @@
         <v>1</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -7400,17 +7400,17 @@
         <v>1</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
@@ -7421,17 +7421,17 @@
         <v>1</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
@@ -7442,17 +7442,17 @@
         <v>1</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
@@ -7463,17 +7463,17 @@
         <v>1</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
@@ -7484,17 +7484,17 @@
         <v>1</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -7505,17 +7505,17 @@
         <v>1</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -7526,17 +7526,17 @@
         <v>1</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -9225,7 +9225,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C3" s="4" t="b">
         <v>0</v>
@@ -9237,19 +9237,19 @@
         <v>61</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>260</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>261</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
@@ -9259,7 +9259,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C4" s="4" t="b">
         <v>0</v>
@@ -9271,19 +9271,19 @@
         <v>61</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>267</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -9293,7 +9293,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C5" s="4" t="b">
         <v>0</v>
@@ -9305,19 +9305,19 @@
         <v>61</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>272</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>273</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -9327,7 +9327,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C6" s="4" t="b">
         <v>0</v>
@@ -9339,19 +9339,19 @@
         <v>61</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -9361,7 +9361,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C7" s="4" t="b">
         <v>0</v>
@@ -9373,19 +9373,19 @@
         <v>61</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I7" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -9395,7 +9395,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C8" s="4" t="b">
         <v>0</v>
@@ -9407,19 +9407,19 @@
         <v>61</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -9429,7 +9429,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C9" s="4" t="b">
         <v>0</v>
@@ -9441,19 +9441,19 @@
         <v>61</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>292</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>293</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -9463,7 +9463,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C10" s="4" t="b">
         <v>0</v>
@@ -9475,19 +9475,19 @@
         <v>61</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>298</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -9497,7 +9497,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C11" s="4" t="b">
         <v>0</v>
@@ -9509,19 +9509,19 @@
         <v>61</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I11" s="5" t="s">
+      <c r="J11" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>303</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -9531,7 +9531,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C12" s="4" t="b">
         <v>0</v>
@@ -9543,19 +9543,19 @@
         <v>61</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="I12" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="J12" s="5" t="s">
         <v>308</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>309</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -9565,7 +9565,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C13" s="4" t="b">
         <v>0</v>
@@ -9577,19 +9577,19 @@
         <v>61</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>312</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>313</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -9599,7 +9599,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C14" s="4" t="b">
         <v>0</v>
@@ -9611,13 +9611,13 @@
         <v>61</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>316</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>317</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -9629,7 +9629,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C15" s="4" t="b">
         <v>0</v>
@@ -9641,19 +9641,19 @@
         <v>61</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="I15" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="J15" s="5" t="s">
         <v>321</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>322</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -9663,7 +9663,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="4" t="b">
         <v>0</v>
@@ -9675,16 +9675,16 @@
         <v>61</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="I16" s="5" t="s">
         <v>326</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>327</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -9695,7 +9695,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C17" s="4" t="b">
         <v>0</v>
@@ -9707,16 +9707,16 @@
         <v>61</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>330</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>331</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -9727,7 +9727,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C18" s="4" t="b">
         <v>0</v>
@@ -9739,19 +9739,19 @@
         <v>61</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I18" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>334</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>335</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
@@ -9761,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C19" s="4" t="b">
         <v>0</v>
@@ -9773,19 +9773,19 @@
         <v>61</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="I19" s="5" t="s">
+      <c r="J19" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>340</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
@@ -9795,7 +9795,7 @@
         <v>1</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C20" s="4" t="b">
         <v>0</v>
@@ -9807,19 +9807,19 @@
         <v>61</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I20" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I20" s="5" t="s">
+      <c r="J20" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>345</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
@@ -9829,7 +9829,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C21" s="4" t="b">
         <v>0</v>
@@ -9841,19 +9841,19 @@
         <v>61</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I21" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="H21" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="I21" s="5" t="s">
+      <c r="J21" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>350</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
@@ -9863,7 +9863,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C22" s="4" t="b">
         <v>0</v>
@@ -9872,16 +9872,16 @@
         <v>2020</v>
       </c>
       <c r="E22" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>352</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
@@ -9893,7 +9893,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C23" s="4" t="b">
         <v>0</v>
@@ -9905,16 +9905,16 @@
         <v>61</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -9925,7 +9925,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C24" s="4" t="b">
         <v>0</v>
@@ -9937,19 +9937,19 @@
         <v>61</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="H24" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I24" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="H24" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="I24" s="5" t="s">
+      <c r="J24" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>364</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -9959,7 +9959,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C25" s="4" t="b">
         <v>0</v>
@@ -9971,16 +9971,16 @@
         <v>61</v>
       </c>
       <c r="F25" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="I25" s="5" t="s">
         <v>368</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>369</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -9991,7 +9991,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C26" s="4" t="b">
         <v>0</v>
@@ -10003,19 +10003,19 @@
         <v>61</v>
       </c>
       <c r="F26" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="I26" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="I26" s="5" t="s">
+      <c r="J26" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>373</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -10025,7 +10025,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C27" s="4" t="b">
         <v>0</v>
@@ -10037,16 +10037,16 @@
         <v>61</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="I27" s="5" t="s">
         <v>376</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>377</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -10057,7 +10057,7 @@
         <v>1</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C28" s="4" t="b">
         <v>0</v>
@@ -10069,19 +10069,19 @@
         <v>61</v>
       </c>
       <c r="F28" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="I28" s="5" t="s">
+      <c r="J28" s="5" t="s">
         <v>381</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>382</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
@@ -10091,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C29" s="4" t="b">
         <v>0</v>
@@ -10100,16 +10100,16 @@
         <v>2019</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>385</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>386</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
@@ -10121,7 +10121,7 @@
         <v>1</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C30" s="4" t="b">
         <v>0</v>
@@ -10130,16 +10130,16 @@
         <v>2019</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -10151,7 +10151,7 @@
         <v>1</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C31" s="4" t="b">
         <v>0</v>
@@ -10163,13 +10163,13 @@
         <v>61</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>391</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>392</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
@@ -10181,7 +10181,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C32" s="4" t="b">
         <v>0</v>
@@ -10193,16 +10193,16 @@
         <v>61</v>
       </c>
       <c r="F32" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="H32" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="I32" s="5" t="s">
         <v>395</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>396</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
@@ -10213,7 +10213,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C33" s="4" t="b">
         <v>0</v>
@@ -10225,16 +10225,16 @@
         <v>61</v>
       </c>
       <c r="F33" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>400</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>401</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -10245,7 +10245,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C34" s="4" t="b">
         <v>0</v>
@@ -10257,16 +10257,16 @@
         <v>61</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
@@ -10277,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C35" s="4" t="b">
         <v>0</v>
@@ -10286,16 +10286,16 @@
         <v>2018</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F35" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>406</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>407</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
@@ -10307,7 +10307,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C36" s="4" t="b">
         <v>0</v>
@@ -10316,16 +10316,16 @@
         <v>2018</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
@@ -10337,7 +10337,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C37" s="4" t="b">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>61</v>
       </c>
       <c r="F37" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H37" s="5" t="s">
         <v>410</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>411</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
@@ -10367,7 +10367,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C38" s="4" t="b">
         <v>0</v>
@@ -10379,19 +10379,19 @@
         <v>61</v>
       </c>
       <c r="F38" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="J38" s="5" t="s">
         <v>416</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>417</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
@@ -10401,7 +10401,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C39" s="4" t="b">
         <v>0</v>
@@ -10413,19 +10413,19 @@
         <v>61</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I39" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="J39" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>421</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
@@ -10435,7 +10435,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C40" s="4" t="b">
         <v>0</v>
@@ -10447,16 +10447,16 @@
         <v>61</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
@@ -10467,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C41" s="4" t="b">
         <v>0</v>
@@ -10476,16 +10476,16 @@
         <v>2017</v>
       </c>
       <c r="E41" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="F41" s="5" t="s">
-        <v>427</v>
-      </c>
       <c r="G41" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
@@ -10497,7 +10497,7 @@
         <v>1</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C42" s="4" t="b">
         <v>0</v>
@@ -10506,16 +10506,16 @@
         <v>2017</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
@@ -10527,7 +10527,7 @@
         <v>1</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C43" s="4" t="b">
         <v>0</v>
@@ -10539,16 +10539,16 @@
         <v>61</v>
       </c>
       <c r="F43" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="H43" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="I43" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>433</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
@@ -10559,7 +10559,7 @@
         <v>1</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C44" s="4" t="b">
         <v>0</v>
@@ -10571,16 +10571,16 @@
         <v>61</v>
       </c>
       <c r="F44" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="H44" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="I44" s="5" t="s">
         <v>436</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>437</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
@@ -10591,7 +10591,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C45" s="4" t="b">
         <v>0</v>
@@ -10603,16 +10603,16 @@
         <v>61</v>
       </c>
       <c r="F45" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="H45" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="I45" s="5" t="s">
         <v>441</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>442</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
@@ -10623,7 +10623,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C46" s="4" t="b">
         <v>0</v>
@@ -10632,16 +10632,16 @@
         <v>2016</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F46" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>445</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
@@ -10653,7 +10653,7 @@
         <v>1</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C47" s="4" t="b">
         <v>0</v>
@@ -10662,16 +10662,16 @@
         <v>2016</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
@@ -10683,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C48" s="4" t="b">
         <v>0</v>
@@ -10692,16 +10692,16 @@
         <v>2016</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
@@ -10713,7 +10713,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C49" s="4" t="b">
         <v>0</v>
@@ -10722,16 +10722,16 @@
         <v>2016</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
@@ -10743,7 +10743,7 @@
         <v>1</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C50" s="4" t="b">
         <v>0</v>
@@ -10755,19 +10755,19 @@
         <v>61</v>
       </c>
       <c r="F50" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="H50" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="I50" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="J50" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="J50" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
@@ -10777,7 +10777,7 @@
         <v>1</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C51" s="4" t="b">
         <v>0</v>
@@ -10789,13 +10789,13 @@
         <v>61</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
@@ -10807,7 +10807,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C52" s="4" t="b">
         <v>0</v>
@@ -10819,16 +10819,16 @@
         <v>61</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H52" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="I52" s="5" t="s">
         <v>463</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>464</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
@@ -10839,7 +10839,7 @@
         <v>1</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C53" s="4" t="b">
         <v>0</v>
@@ -10851,16 +10851,16 @@
         <v>61</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
@@ -10871,7 +10871,7 @@
         <v>1</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C54" s="4" t="b">
         <v>0</v>
@@ -10883,16 +10883,16 @@
         <v>61</v>
       </c>
       <c r="F54" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="I54" s="5" t="s">
         <v>469</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>470</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
@@ -10903,7 +10903,7 @@
         <v>1</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C55" s="4" t="b">
         <v>0</v>
@@ -10915,16 +10915,16 @@
         <v>61</v>
       </c>
       <c r="F55" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="G55" s="5" t="s">
+      <c r="H55" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="I55" s="5" t="s">
         <v>473</v>
-      </c>
-      <c r="H55" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I55" s="5" t="s">
-        <v>474</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
@@ -10935,7 +10935,7 @@
         <v>1</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C56" s="4" t="b">
         <v>0</v>
@@ -10947,19 +10947,19 @@
         <v>61</v>
       </c>
       <c r="F56" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="H56" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="H56" s="5" t="s">
+      <c r="I56" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="I56" s="5" t="s">
+      <c r="J56" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>480</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
@@ -10969,7 +10969,7 @@
         <v>1</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C57" s="4" t="b">
         <v>0</v>
@@ -10978,16 +10978,16 @@
         <v>2015</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
@@ -10999,7 +10999,7 @@
         <v>1</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C58" s="4" t="b">
         <v>0</v>
@@ -11008,16 +11008,16 @@
         <v>2015</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F58" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
@@ -11029,7 +11029,7 @@
         <v>1</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C59" s="4" t="b">
         <v>0</v>
@@ -11038,16 +11038,16 @@
         <v>2015</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
@@ -11059,7 +11059,7 @@
         <v>1</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C60" s="4" t="b">
         <v>0</v>
@@ -11071,19 +11071,19 @@
         <v>61</v>
       </c>
       <c r="F60" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="G60" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="H60" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="H60" s="5" t="s">
+      <c r="I60" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="I60" s="5" t="s">
+      <c r="J60" s="5" t="s">
         <v>491</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>492</v>
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
@@ -11093,7 +11093,7 @@
         <v>1</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C61" s="4" t="b">
         <v>0</v>
@@ -11105,19 +11105,19 @@
         <v>61</v>
       </c>
       <c r="F61" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="G61" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="H61" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="H61" s="5" t="s">
+      <c r="I61" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="I61" s="5" t="s">
+      <c r="J61" s="5" t="s">
         <v>497</v>
-      </c>
-      <c r="J61" s="5" t="s">
-        <v>498</v>
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
@@ -11127,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C62" s="4" t="b">
         <v>0</v>
@@ -11139,19 +11139,19 @@
         <v>61</v>
       </c>
       <c r="F62" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="G62" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="H62" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I62" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="H62" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="I62" s="5" t="s">
+      <c r="J62" s="5" t="s">
         <v>502</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>503</v>
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
@@ -11161,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C63" s="4" t="b">
         <v>0</v>
@@ -11173,16 +11173,16 @@
         <v>61</v>
       </c>
       <c r="F63" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="H63" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="H63" s="5" t="s">
+      <c r="I63" s="5" t="s">
         <v>507</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>508</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
@@ -11193,7 +11193,7 @@
         <v>1</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C64" s="4" t="b">
         <v>0</v>
@@ -11205,16 +11205,16 @@
         <v>61</v>
       </c>
       <c r="F64" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G64" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="H64" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="H64" s="5" t="s">
+      <c r="I64" s="5" t="s">
         <v>512</v>
-      </c>
-      <c r="I64" s="5" t="s">
-        <v>513</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
@@ -11225,7 +11225,7 @@
         <v>1</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C65" s="4" t="b">
         <v>0</v>
@@ -11237,16 +11237,16 @@
         <v>61</v>
       </c>
       <c r="F65" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="G65" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="G65" s="5" t="s">
+      <c r="H65" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="H65" s="5" t="s">
+      <c r="I65" s="5" t="s">
         <v>517</v>
-      </c>
-      <c r="I65" s="5" t="s">
-        <v>518</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
@@ -11257,7 +11257,7 @@
         <v>1</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C66" s="4" t="b">
         <v>0</v>
@@ -11269,19 +11269,19 @@
         <v>61</v>
       </c>
       <c r="F66" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="H66" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="H66" s="5" t="s">
+      <c r="I66" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="I66" s="5" t="s">
+      <c r="J66" s="5" t="s">
         <v>522</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>523</v>
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
@@ -11291,7 +11291,7 @@
         <v>1</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C67" s="4" t="b">
         <v>0</v>
@@ -11303,16 +11303,16 @@
         <v>61</v>
       </c>
       <c r="F67" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="I67" s="5" t="s">
         <v>525</v>
-      </c>
-      <c r="G67" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="H67" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>526</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
@@ -11323,7 +11323,7 @@
         <v>1</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C68" s="4" t="b">
         <v>0</v>
@@ -11335,16 +11335,16 @@
         <v>61</v>
       </c>
       <c r="F68" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="G68" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="H68" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="I68" s="5" t="s">
         <v>529</v>
-      </c>
-      <c r="H68" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="I68" s="5" t="s">
-        <v>530</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
@@ -11355,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C69" s="4" t="b">
         <v>0</v>
@@ -11367,19 +11367,19 @@
         <v>61</v>
       </c>
       <c r="F69" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="G69" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="H69" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I69" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="H69" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="I69" s="5" t="s">
+      <c r="J69" s="5" t="s">
         <v>534</v>
-      </c>
-      <c r="J69" s="5" t="s">
-        <v>535</v>
       </c>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
@@ -11389,7 +11389,7 @@
         <v>1</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C70" s="4" t="b">
         <v>0</v>
@@ -11401,16 +11401,16 @@
         <v>61</v>
       </c>
       <c r="F70" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="G70" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="H70" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="I70" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="H70" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="I70" s="5" t="s">
-        <v>539</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
@@ -11421,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C71" s="4" t="b">
         <v>0</v>
@@ -11430,16 +11430,16 @@
         <v>2014</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
@@ -11451,7 +11451,7 @@
         <v>1</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C72" s="4" t="b">
         <v>0</v>
@@ -11463,16 +11463,16 @@
         <v>61</v>
       </c>
       <c r="F72" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="G72" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="H72" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="H72" s="5" t="s">
+      <c r="I72" s="5" t="s">
         <v>544</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>545</v>
       </c>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
@@ -11483,7 +11483,7 @@
         <v>1</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C73" s="4" t="b">
         <v>0</v>
@@ -11495,16 +11495,16 @@
         <v>61</v>
       </c>
       <c r="F73" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="H73" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="H73" s="5" t="s">
+      <c r="I73" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="I73" s="5" t="s">
-        <v>550</v>
       </c>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
@@ -11515,7 +11515,7 @@
         <v>1</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C74" s="4" t="b">
         <v>0</v>
@@ -11527,16 +11527,16 @@
         <v>61</v>
       </c>
       <c r="F74" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="G74" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="H74" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="H74" s="5" t="s">
+      <c r="I74" s="5" t="s">
         <v>554</v>
-      </c>
-      <c r="I74" s="5" t="s">
-        <v>555</v>
       </c>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
@@ -11547,7 +11547,7 @@
         <v>1</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C75" s="4" t="b">
         <v>0</v>
@@ -11559,16 +11559,16 @@
         <v>61</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
@@ -11579,7 +11579,7 @@
         <v>1</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C76" s="4" t="b">
         <v>0</v>
@@ -11591,16 +11591,16 @@
         <v>61</v>
       </c>
       <c r="F76" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="G76" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="H76" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="H76" s="5" t="s">
+      <c r="I76" s="5" t="s">
         <v>562</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>563</v>
       </c>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
@@ -11611,7 +11611,7 @@
         <v>1</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C77" s="4" t="b">
         <v>0</v>
@@ -11623,16 +11623,16 @@
         <v>61</v>
       </c>
       <c r="F77" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="G77" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="H77" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="I77" s="5" t="s">
         <v>566</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="I77" s="5" t="s">
-        <v>567</v>
       </c>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
@@ -11643,7 +11643,7 @@
         <v>1</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C78" s="4" t="b">
         <v>0</v>
@@ -11652,16 +11652,16 @@
         <v>2013</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -11673,7 +11673,7 @@
         <v>1</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C79" s="4" t="b">
         <v>0</v>
@@ -11685,16 +11685,16 @@
         <v>61</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H79" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="I79" s="5" t="s">
         <v>572</v>
-      </c>
-      <c r="I79" s="5" t="s">
-        <v>573</v>
       </c>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
@@ -11705,7 +11705,7 @@
         <v>1</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C80" s="4" t="b">
         <v>0</v>
@@ -11717,16 +11717,16 @@
         <v>61</v>
       </c>
       <c r="F80" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H80" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H80" s="5" t="s">
+      <c r="I80" s="5" t="s">
         <v>576</v>
-      </c>
-      <c r="I80" s="5" t="s">
-        <v>577</v>
       </c>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
@@ -11737,7 +11737,7 @@
         <v>1</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C81" s="4" t="b">
         <v>0</v>
@@ -11749,16 +11749,16 @@
         <v>61</v>
       </c>
       <c r="F81" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="G81" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="G81" s="5" t="s">
+      <c r="H81" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="H81" s="5" t="s">
+      <c r="I81" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="I81" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
@@ -11769,7 +11769,7 @@
         <v>1</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C82" s="4" t="b">
         <v>0</v>
@@ -11781,16 +11781,16 @@
         <v>61</v>
       </c>
       <c r="F82" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="G82" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="H82" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="I82" s="5" t="s">
         <v>585</v>
-      </c>
-      <c r="H82" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>586</v>
       </c>
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
@@ -11801,7 +11801,7 @@
         <v>1</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C83" s="4" t="b">
         <v>0</v>
@@ -11813,16 +11813,16 @@
         <v>61</v>
       </c>
       <c r="F83" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="G83" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="H83" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="H83" s="5" t="s">
+      <c r="I83" s="5" t="s">
         <v>590</v>
-      </c>
-      <c r="I83" s="5" t="s">
-        <v>591</v>
       </c>
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
@@ -11833,7 +11833,7 @@
         <v>1</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C84" s="4" t="b">
         <v>0</v>
@@ -11845,16 +11845,16 @@
         <v>61</v>
       </c>
       <c r="F84" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="G84" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="G84" s="5" t="s">
+      <c r="H84" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I84" s="5" t="s">
         <v>594</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="I84" s="5" t="s">
-        <v>595</v>
       </c>
       <c r="J84" s="5"/>
       <c r="K84" s="5"/>
@@ -11865,7 +11865,7 @@
         <v>1</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C85" s="4" t="b">
         <v>0</v>
@@ -11877,16 +11877,16 @@
         <v>61</v>
       </c>
       <c r="F85" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="G85" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="G85" s="5" t="s">
+      <c r="H85" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="H85" s="5" t="s">
+      <c r="I85" s="5" t="s">
         <v>599</v>
-      </c>
-      <c r="I85" s="5" t="s">
-        <v>600</v>
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="5"/>
@@ -11897,7 +11897,7 @@
         <v>1</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C86" s="4" t="b">
         <v>0</v>
@@ -11906,16 +11906,16 @@
         <v>2012</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
@@ -11927,7 +11927,7 @@
         <v>1</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C87" s="4" t="b">
         <v>0</v>
@@ -11936,16 +11936,16 @@
         <v>2012</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G87" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
@@ -11957,7 +11957,7 @@
         <v>1</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C88" s="4" t="b">
         <v>0</v>
@@ -11969,16 +11969,16 @@
         <v>61</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G88" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H88" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="I88" s="5" t="s">
         <v>608</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>609</v>
       </c>
       <c r="J88" s="5"/>
       <c r="K88" s="5"/>
@@ -11989,7 +11989,7 @@
         <v>1</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C89" s="4" t="b">
         <v>0</v>
@@ -12001,13 +12001,13 @@
         <v>61</v>
       </c>
       <c r="F89" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H89" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>612</v>
       </c>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
@@ -12019,7 +12019,7 @@
         <v>1</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C90" s="4" t="b">
         <v>0</v>
@@ -12031,16 +12031,16 @@
         <v>61</v>
       </c>
       <c r="F90" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="G90" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="H90" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="I90" s="5" t="s">
         <v>615</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>616</v>
       </c>
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
@@ -12051,7 +12051,7 @@
         <v>1</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C91" s="4" t="b">
         <v>0</v>
@@ -12063,19 +12063,19 @@
         <v>61</v>
       </c>
       <c r="F91" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H91" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="H91" s="5" t="s">
+      <c r="I91" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="I91" s="5" t="s">
+      <c r="J91" s="5" t="s">
         <v>620</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>621</v>
       </c>
       <c r="K91" s="5"/>
       <c r="L91" s="5"/>
@@ -12085,7 +12085,7 @@
         <v>1</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C92" s="4" t="b">
         <v>0</v>
@@ -12097,16 +12097,16 @@
         <v>61</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G92" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H92" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="I92" s="5" t="s">
         <v>624</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>625</v>
       </c>
       <c r="J92" s="5"/>
       <c r="K92" s="5"/>
@@ -12117,7 +12117,7 @@
         <v>1</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C93" s="4" t="b">
         <v>0</v>
@@ -12129,16 +12129,16 @@
         <v>61</v>
       </c>
       <c r="F93" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H93" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H93" s="5" t="s">
+      <c r="I93" s="5" t="s">
         <v>628</v>
-      </c>
-      <c r="I93" s="5" t="s">
-        <v>629</v>
       </c>
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
@@ -12149,7 +12149,7 @@
         <v>1</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C94" s="4" t="b">
         <v>0</v>
@@ -12161,16 +12161,16 @@
         <v>61</v>
       </c>
       <c r="F94" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H94" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="G94" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H94" s="5" t="s">
+      <c r="I94" s="5" t="s">
         <v>632</v>
-      </c>
-      <c r="I94" s="5" t="s">
-        <v>633</v>
       </c>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
@@ -12181,7 +12181,7 @@
         <v>1</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C95" s="4" t="b">
         <v>0</v>
@@ -12190,16 +12190,16 @@
         <v>2011</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
@@ -12211,7 +12211,7 @@
         <v>1</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C96" s="4" t="b">
         <v>0</v>
@@ -12223,19 +12223,19 @@
         <v>61</v>
       </c>
       <c r="F96" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="G96" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="H96" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="H96" s="5" t="s">
+      <c r="I96" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="I96" s="5" t="s">
+      <c r="J96" s="5" t="s">
         <v>640</v>
-      </c>
-      <c r="J96" s="5" t="s">
-        <v>641</v>
       </c>
       <c r="K96" s="5"/>
       <c r="L96" s="5"/>
@@ -12245,7 +12245,7 @@
         <v>1</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C97" s="4" t="b">
         <v>0</v>
@@ -12257,13 +12257,13 @@
         <v>61</v>
       </c>
       <c r="F97" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H97" s="5" t="s">
         <v>643</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H97" s="5" t="s">
-        <v>644</v>
       </c>
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
@@ -12275,7 +12275,7 @@
         <v>1</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C98" s="4" t="b">
         <v>0</v>
@@ -12287,16 +12287,16 @@
         <v>61</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H98" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="I98" s="5" t="s">
         <v>647</v>
-      </c>
-      <c r="I98" s="5" t="s">
-        <v>648</v>
       </c>
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
@@ -12307,7 +12307,7 @@
         <v>1</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C99" s="4" t="b">
         <v>0</v>
@@ -12319,16 +12319,16 @@
         <v>61</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G99" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H99" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="I99" s="5" t="s">
         <v>651</v>
-      </c>
-      <c r="I99" s="5" t="s">
-        <v>652</v>
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
@@ -12339,7 +12339,7 @@
         <v>1</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C100" s="4" t="b">
         <v>0</v>
@@ -12351,16 +12351,16 @@
         <v>61</v>
       </c>
       <c r="F100" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="G100" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="H100" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I100" s="5" t="s">
         <v>655</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I100" s="5" t="s">
-        <v>656</v>
       </c>
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
@@ -12371,7 +12371,7 @@
         <v>1</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C101" s="4" t="b">
         <v>0</v>
@@ -12383,16 +12383,16 @@
         <v>61</v>
       </c>
       <c r="F101" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="G101" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="H101" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I101" s="5" t="s">
         <v>659</v>
-      </c>
-      <c r="H101" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I101" s="5" t="s">
-        <v>660</v>
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
@@ -12403,7 +12403,7 @@
         <v>1</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C102" s="4" t="b">
         <v>0</v>
@@ -12415,16 +12415,16 @@
         <v>61</v>
       </c>
       <c r="F102" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="G102" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="H102" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I102" s="5" t="s">
         <v>663</v>
-      </c>
-      <c r="H102" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>664</v>
       </c>
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
@@ -12435,7 +12435,7 @@
         <v>1</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C103" s="4" t="b">
         <v>0</v>
@@ -12447,16 +12447,16 @@
         <v>61</v>
       </c>
       <c r="F103" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="G103" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="H103" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I103" s="5" t="s">
         <v>667</v>
-      </c>
-      <c r="H103" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I103" s="5" t="s">
-        <v>668</v>
       </c>
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
@@ -12467,7 +12467,7 @@
         <v>1</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C104" s="4" t="b">
         <v>0</v>
@@ -12479,16 +12479,16 @@
         <v>61</v>
       </c>
       <c r="F104" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="G104" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="H104" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I104" s="5" t="s">
         <v>671</v>
-      </c>
-      <c r="H104" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I104" s="5" t="s">
-        <v>672</v>
       </c>
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
@@ -12499,7 +12499,7 @@
         <v>1</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C105" s="4" t="b">
         <v>0</v>
@@ -12511,16 +12511,16 @@
         <v>61</v>
       </c>
       <c r="F105" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="G105" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="H105" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="I105" s="5" t="s">
         <v>675</v>
-      </c>
-      <c r="H105" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="I105" s="5" t="s">
-        <v>676</v>
       </c>
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
@@ -12531,7 +12531,7 @@
         <v>1</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C106" s="4" t="b">
         <v>0</v>
@@ -12540,16 +12540,16 @@
         <v>2010</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G106" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
@@ -12561,7 +12561,7 @@
         <v>1</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C107" s="4" t="b">
         <v>0</v>
@@ -12573,16 +12573,16 @@
         <v>61</v>
       </c>
       <c r="F107" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H107" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="G107" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H107" s="5" t="s">
+      <c r="I107" s="5" t="s">
         <v>681</v>
-      </c>
-      <c r="I107" s="5" t="s">
-        <v>682</v>
       </c>
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
@@ -12593,7 +12593,7 @@
         <v>1</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C108" s="4" t="b">
         <v>0</v>
@@ -12605,16 +12605,16 @@
         <v>61</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G108" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
@@ -12625,7 +12625,7 @@
         <v>1</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C109" s="4" t="b">
         <v>0</v>
@@ -12637,16 +12637,16 @@
         <v>61</v>
       </c>
       <c r="F109" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="G109" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="H109" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I109" s="5" t="s">
         <v>688</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I109" s="5" t="s">
-        <v>689</v>
       </c>
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
@@ -12657,7 +12657,7 @@
         <v>1</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C110" s="4" t="b">
         <v>0</v>
@@ -12669,16 +12669,16 @@
         <v>61</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G110" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="J110" s="5"/>
       <c r="K110" s="5"/>
@@ -12689,7 +12689,7 @@
         <v>1</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C111" s="4" t="b">
         <v>0</v>
@@ -12701,16 +12701,16 @@
         <v>61</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G111" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="5"/>
@@ -12721,7 +12721,7 @@
         <v>1</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C112" s="4" t="b">
         <v>0</v>
@@ -12733,16 +12733,16 @@
         <v>61</v>
       </c>
       <c r="F112" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="G112" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="H112" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I112" s="5" t="s">
         <v>698</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>699</v>
       </c>
       <c r="J112" s="5"/>
       <c r="K112" s="5"/>
@@ -12753,7 +12753,7 @@
         <v>1</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C113" s="4" t="b">
         <v>0</v>
@@ -12765,16 +12765,16 @@
         <v>61</v>
       </c>
       <c r="F113" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="G113" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="H113" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I113" s="5" t="s">
         <v>702</v>
-      </c>
-      <c r="H113" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I113" s="5" t="s">
-        <v>703</v>
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
@@ -12785,7 +12785,7 @@
         <v>1</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C114" s="4" t="b">
         <v>0</v>
@@ -12797,16 +12797,16 @@
         <v>61</v>
       </c>
       <c r="F114" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I114" s="5" t="s">
         <v>705</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I114" s="5" t="s">
-        <v>706</v>
       </c>
       <c r="J114" s="5"/>
       <c r="K114" s="5"/>
@@ -12817,7 +12817,7 @@
         <v>1</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C115" s="4" t="b">
         <v>0</v>
@@ -12829,16 +12829,16 @@
         <v>61</v>
       </c>
       <c r="F115" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="H115" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="G115" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="H115" s="5" t="s">
+      <c r="I115" s="5" t="s">
         <v>709</v>
-      </c>
-      <c r="I115" s="5" t="s">
-        <v>710</v>
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="5"/>
@@ -12849,7 +12849,7 @@
         <v>1</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C116" s="4" t="b">
         <v>0</v>
@@ -12861,16 +12861,16 @@
         <v>61</v>
       </c>
       <c r="F116" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="G116" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="G116" s="5" t="s">
+      <c r="H116" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I116" s="5" t="s">
         <v>713</v>
-      </c>
-      <c r="H116" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I116" s="5" t="s">
-        <v>714</v>
       </c>
       <c r="J116" s="5"/>
       <c r="K116" s="5"/>
@@ -12881,7 +12881,7 @@
         <v>1</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C117" s="4" t="b">
         <v>0</v>
@@ -12893,19 +12893,19 @@
         <v>61</v>
       </c>
       <c r="F117" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="I117" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="G117" s="5" t="s">
-        <v>675</v>
-      </c>
-      <c r="H117" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="I117" s="5" t="s">
+      <c r="J117" s="5" t="s">
         <v>717</v>
-      </c>
-      <c r="J117" s="5" t="s">
-        <v>718</v>
       </c>
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
@@ -12915,7 +12915,7 @@
         <v>1</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C118" s="4" t="b">
         <v>0</v>
@@ -12927,16 +12927,16 @@
         <v>61</v>
       </c>
       <c r="F118" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I118" s="5" t="s">
         <v>720</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>675</v>
-      </c>
-      <c r="H118" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I118" s="5" t="s">
-        <v>721</v>
       </c>
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
@@ -12947,7 +12947,7 @@
         <v>1</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C119" s="4" t="b">
         <v>0</v>
@@ -12959,16 +12959,16 @@
         <v>61</v>
       </c>
       <c r="F119" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="G119" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="G119" s="5" t="s">
+      <c r="H119" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I119" s="5" t="s">
         <v>724</v>
-      </c>
-      <c r="H119" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I119" s="5" t="s">
-        <v>725</v>
       </c>
       <c r="J119" s="5"/>
       <c r="K119" s="5"/>
@@ -12979,7 +12979,7 @@
         <v>1</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C120" s="4" t="b">
         <v>0</v>
@@ -12991,16 +12991,16 @@
         <v>61</v>
       </c>
       <c r="F120" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="G120" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="G120" s="5" t="s">
+      <c r="H120" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I120" s="5" t="s">
         <v>728</v>
-      </c>
-      <c r="H120" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I120" s="5" t="s">
-        <v>729</v>
       </c>
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
@@ -13011,7 +13011,7 @@
         <v>1</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C121" s="4" t="b">
         <v>0</v>
@@ -13020,16 +13020,16 @@
         <v>2009</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
@@ -13041,7 +13041,7 @@
         <v>1</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C122" s="4" t="b">
         <v>0</v>
@@ -13050,16 +13050,16 @@
         <v>2009</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
@@ -13071,7 +13071,7 @@
         <v>1</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C123" s="4" t="b">
         <v>0</v>
@@ -13080,16 +13080,16 @@
         <v>2009</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
@@ -13101,7 +13101,7 @@
         <v>1</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C124" s="4" t="b">
         <v>0</v>
@@ -13110,16 +13110,16 @@
         <v>2009</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G124" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
@@ -13131,7 +13131,7 @@
         <v>1</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C125" s="4" t="b">
         <v>0</v>
@@ -13140,16 +13140,16 @@
         <v>2009</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G125" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
@@ -13161,7 +13161,7 @@
         <v>1</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C126" s="4" t="b">
         <v>0</v>
@@ -13170,16 +13170,16 @@
         <v>2009</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
@@ -13191,7 +13191,7 @@
         <v>1</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C127" s="4" t="b">
         <v>0</v>
@@ -13200,16 +13200,16 @@
         <v>2009</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G127" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
@@ -13221,7 +13221,7 @@
         <v>1</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C128" s="4" t="b">
         <v>0</v>
@@ -13230,16 +13230,16 @@
         <v>2009</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
@@ -13251,7 +13251,7 @@
         <v>1</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C129" s="4" t="b">
         <v>0</v>
@@ -13260,16 +13260,16 @@
         <v>2009</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G129" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
@@ -13281,7 +13281,7 @@
         <v>1</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C130" s="4" t="b">
         <v>0</v>
@@ -13290,16 +13290,16 @@
         <v>2009</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G130" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
@@ -13311,7 +13311,7 @@
         <v>1</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C131" s="4" t="b">
         <v>0</v>
@@ -13320,16 +13320,16 @@
         <v>2009</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
@@ -13341,7 +13341,7 @@
         <v>1</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C132" s="4" t="b">
         <v>0</v>
@@ -13350,16 +13350,16 @@
         <v>2009</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G132" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
@@ -13371,7 +13371,7 @@
         <v>1</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C133" s="4" t="b">
         <v>0</v>
@@ -13383,16 +13383,16 @@
         <v>61</v>
       </c>
       <c r="F133" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="G133" s="5" t="s">
         <v>750</v>
       </c>
-      <c r="G133" s="5" t="s">
+      <c r="H133" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I133" s="5" t="s">
         <v>751</v>
-      </c>
-      <c r="H133" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I133" s="5" t="s">
-        <v>752</v>
       </c>
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
@@ -13403,7 +13403,7 @@
         <v>1</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C134" s="4" t="b">
         <v>0</v>
@@ -13415,16 +13415,16 @@
         <v>61</v>
       </c>
       <c r="F134" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="G134" s="5" t="s">
         <v>754</v>
       </c>
-      <c r="G134" s="5" t="s">
+      <c r="H134" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I134" s="5" t="s">
         <v>755</v>
-      </c>
-      <c r="H134" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I134" s="5" t="s">
-        <v>756</v>
       </c>
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
@@ -13435,7 +13435,7 @@
         <v>1</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C135" s="4" t="b">
         <v>0</v>
@@ -13447,16 +13447,16 @@
         <v>61</v>
       </c>
       <c r="F135" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="G135" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="G135" s="5" t="s">
+      <c r="H135" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I135" s="5" t="s">
         <v>759</v>
-      </c>
-      <c r="H135" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I135" s="5" t="s">
-        <v>760</v>
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
@@ -13467,7 +13467,7 @@
         <v>1</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C136" s="4" t="b">
         <v>0</v>
@@ -13479,16 +13479,16 @@
         <v>61</v>
       </c>
       <c r="F136" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="G136" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="G136" s="5" t="s">
+      <c r="H136" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I136" s="5" t="s">
         <v>763</v>
-      </c>
-      <c r="H136" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I136" s="5" t="s">
-        <v>764</v>
       </c>
       <c r="J136" s="5"/>
       <c r="K136" s="5"/>
@@ -13499,7 +13499,7 @@
         <v>1</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C137" s="4" t="b">
         <v>0</v>
@@ -13508,16 +13508,16 @@
         <v>2008</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F137" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H137" s="5" t="s">
         <v>766</v>
-      </c>
-      <c r="G137" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H137" s="5" t="s">
-        <v>767</v>
       </c>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
@@ -13529,7 +13529,7 @@
         <v>1</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C138" s="4" t="b">
         <v>0</v>
@@ -13541,16 +13541,16 @@
         <v>61</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H138" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="I138" s="5" t="s">
         <v>770</v>
-      </c>
-      <c r="I138" s="5" t="s">
-        <v>771</v>
       </c>
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
@@ -13561,7 +13561,7 @@
         <v>1</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C139" s="4" t="b">
         <v>0</v>
@@ -13573,16 +13573,16 @@
         <v>61</v>
       </c>
       <c r="F139" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H139" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="G139" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H139" s="5" t="s">
+      <c r="I139" s="5" t="s">
         <v>774</v>
-      </c>
-      <c r="I139" s="5" t="s">
-        <v>775</v>
       </c>
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
@@ -13593,7 +13593,7 @@
         <v>1</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C140" s="4" t="b">
         <v>0</v>
@@ -13605,16 +13605,16 @@
         <v>61</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H140" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="I140" s="5" t="s">
         <v>778</v>
-      </c>
-      <c r="I140" s="5" t="s">
-        <v>779</v>
       </c>
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
@@ -13625,7 +13625,7 @@
         <v>1</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C141" s="4" t="b">
         <v>0</v>
@@ -13637,16 +13637,16 @@
         <v>61</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H141" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="I141" s="5" t="s">
         <v>782</v>
-      </c>
-      <c r="I141" s="5" t="s">
-        <v>783</v>
       </c>
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
@@ -13657,7 +13657,7 @@
         <v>1</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C142" s="4" t="b">
         <v>0</v>
@@ -13669,16 +13669,16 @@
         <v>61</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="I142" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
@@ -13689,7 +13689,7 @@
         <v>1</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C143" s="4" t="b">
         <v>0</v>
@@ -13701,16 +13701,16 @@
         <v>61</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H143" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="I143" s="5" t="s">
         <v>789</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>790</v>
       </c>
       <c r="J143" s="5"/>
       <c r="K143" s="5"/>
@@ -13721,7 +13721,7 @@
         <v>1</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C144" s="4" t="b">
         <v>0</v>
@@ -13733,16 +13733,16 @@
         <v>61</v>
       </c>
       <c r="F144" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>792</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="H144" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="I144" s="5" t="s">
-        <v>793</v>
       </c>
       <c r="J144" s="5"/>
       <c r="K144" s="5"/>
@@ -13753,7 +13753,7 @@
         <v>1</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C145" s="4" t="b">
         <v>0</v>
@@ -13762,16 +13762,16 @@
         <v>2007</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F145" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H145" s="5" t="s">
         <v>795</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H145" s="5" t="s">
-        <v>796</v>
       </c>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
@@ -13783,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C146" s="4" t="b">
         <v>0</v>
@@ -13792,16 +13792,16 @@
         <v>2007</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F146" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H146" s="5" t="s">
         <v>798</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H146" s="5" t="s">
-        <v>799</v>
       </c>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
@@ -13813,7 +13813,7 @@
         <v>1</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C147" s="4" t="b">
         <v>0</v>
@@ -13822,16 +13822,16 @@
         <v>2007</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G147" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
@@ -13843,7 +13843,7 @@
         <v>1</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C148" s="4" t="b">
         <v>0</v>
@@ -13852,16 +13852,16 @@
         <v>2007</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G148" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
@@ -13873,7 +13873,7 @@
         <v>1</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C149" s="4" t="b">
         <v>0</v>
@@ -13882,16 +13882,16 @@
         <v>2007</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G149" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
@@ -13903,7 +13903,7 @@
         <v>1</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C150" s="4" t="b">
         <v>0</v>
@@ -13915,13 +13915,13 @@
         <v>61</v>
       </c>
       <c r="F150" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H150" s="5" t="s">
         <v>809</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H150" s="5" t="s">
-        <v>810</v>
       </c>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
@@ -13933,7 +13933,7 @@
         <v>1</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C151" s="4" t="b">
         <v>0</v>
@@ -13945,16 +13945,16 @@
         <v>61</v>
       </c>
       <c r="F151" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="G151" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="G151" s="5" t="s">
+      <c r="H151" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="I151" s="5" t="s">
         <v>813</v>
-      </c>
-      <c r="H151" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="I151" s="5" t="s">
-        <v>814</v>
       </c>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
@@ -13965,7 +13965,7 @@
         <v>1</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C152" s="4" t="b">
         <v>0</v>
@@ -13977,16 +13977,16 @@
         <v>61</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H152" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="I152" s="5" t="s">
         <v>817</v>
-      </c>
-      <c r="I152" s="5" t="s">
-        <v>818</v>
       </c>
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
@@ -13997,7 +13997,7 @@
         <v>1</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C153" s="4" t="b">
         <v>0</v>
@@ -14009,16 +14009,16 @@
         <v>61</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G153" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I153" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
@@ -14029,7 +14029,7 @@
         <v>1</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C154" s="4" t="b">
         <v>0</v>
@@ -14041,16 +14041,16 @@
         <v>61</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H154" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="I154" s="5" t="s">
         <v>824</v>
-      </c>
-      <c r="I154" s="5" t="s">
-        <v>825</v>
       </c>
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
@@ -14061,7 +14061,7 @@
         <v>1</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C155" s="4" t="b">
         <v>0</v>
@@ -14073,13 +14073,13 @@
         <v>61</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
@@ -14091,7 +14091,7 @@
         <v>1</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C156" s="4" t="b">
         <v>0</v>
@@ -14103,16 +14103,16 @@
         <v>61</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G156" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
@@ -14123,7 +14123,7 @@
         <v>1</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C157" s="4" t="b">
         <v>0</v>
@@ -14135,16 +14135,16 @@
         <v>61</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H157" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="I157" s="5" t="s">
         <v>834</v>
-      </c>
-      <c r="I157" s="5" t="s">
-        <v>835</v>
       </c>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
@@ -14155,7 +14155,7 @@
         <v>1</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C158" s="4" t="b">
         <v>0</v>
@@ -14167,16 +14167,16 @@
         <v>61</v>
       </c>
       <c r="F158" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="I158" s="5" t="s">
         <v>837</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="H158" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="I158" s="5" t="s">
-        <v>838</v>
       </c>
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
@@ -14187,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C159" s="4" t="b">
         <v>0</v>
@@ -14199,16 +14199,16 @@
         <v>61</v>
       </c>
       <c r="F159" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="G159" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="G159" s="5" t="s">
+      <c r="H159" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="I159" s="5" t="s">
         <v>841</v>
-      </c>
-      <c r="H159" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I159" s="5" t="s">
-        <v>842</v>
       </c>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
@@ -14219,7 +14219,7 @@
         <v>1</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C160" s="4" t="b">
         <v>0</v>
@@ -14231,16 +14231,16 @@
         <v>61</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
@@ -14251,7 +14251,7 @@
         <v>1</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C161" s="4" t="b">
         <v>0</v>
@@ -14263,16 +14263,16 @@
         <v>61</v>
       </c>
       <c r="F161" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H161" s="5" t="s">
         <v>847</v>
       </c>
-      <c r="G161" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H161" s="5" t="s">
-        <v>848</v>
-      </c>
       <c r="I161" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
@@ -14283,7 +14283,7 @@
         <v>1</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C162" s="4" t="b">
         <v>0</v>
@@ -14295,13 +14295,13 @@
         <v>61</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G162" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
@@ -14313,7 +14313,7 @@
         <v>1</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C163" s="4" t="b">
         <v>0</v>
@@ -14322,16 +14322,16 @@
         <v>2005</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F163" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H163" s="5" t="s">
         <v>853</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H163" s="5" t="s">
-        <v>854</v>
       </c>
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
@@ -14343,7 +14343,7 @@
         <v>1</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C164" s="4" t="b">
         <v>0</v>
@@ -14355,13 +14355,13 @@
         <v>61</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G164" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
@@ -14373,7 +14373,7 @@
         <v>1</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C165" s="4" t="b">
         <v>0</v>
@@ -14385,16 +14385,16 @@
         <v>61</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G165" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H165" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="I165" s="5" t="s">
         <v>860</v>
-      </c>
-      <c r="I165" s="5" t="s">
-        <v>861</v>
       </c>
       <c r="J165" s="5"/>
       <c r="K165" s="5"/>
@@ -14405,7 +14405,7 @@
         <v>1</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C166" s="4" t="b">
         <v>0</v>
@@ -14417,16 +14417,16 @@
         <v>61</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G166" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H166" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="I166" s="5" t="s">
         <v>864</v>
-      </c>
-      <c r="I166" s="5" t="s">
-        <v>865</v>
       </c>
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
@@ -14437,7 +14437,7 @@
         <v>1</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C167" s="4" t="b">
         <v>0</v>
@@ -14449,16 +14449,16 @@
         <v>61</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I167" s="5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
@@ -14469,7 +14469,7 @@
         <v>1</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C168" s="4" t="b">
         <v>0</v>
@@ -14481,16 +14481,16 @@
         <v>61</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G168" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="I168" s="5" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J168" s="5"/>
       <c r="K168" s="5"/>
@@ -14501,7 +14501,7 @@
         <v>1</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C169" s="4" t="b">
         <v>0</v>
@@ -14510,16 +14510,16 @@
         <v>2004</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F169" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H169" s="5" t="s">
         <v>873</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H169" s="5" t="s">
-        <v>874</v>
       </c>
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
@@ -14531,7 +14531,7 @@
         <v>1</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C170" s="4" t="b">
         <v>0</v>
@@ -14540,16 +14540,16 @@
         <v>2004</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G170" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
@@ -14561,7 +14561,7 @@
         <v>1</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C171" s="4" t="b">
         <v>0</v>
@@ -14570,16 +14570,16 @@
         <v>2004</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
@@ -14591,7 +14591,7 @@
         <v>1</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C172" s="4" t="b">
         <v>0</v>
@@ -14600,16 +14600,16 @@
         <v>2004</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
@@ -14621,7 +14621,7 @@
         <v>1</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C173" s="4" t="b">
         <v>0</v>
@@ -14630,16 +14630,16 @@
         <v>2004</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G173" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
@@ -14651,7 +14651,7 @@
         <v>1</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C174" s="4" t="b">
         <v>0</v>
@@ -14660,16 +14660,16 @@
         <v>2004</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G174" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
@@ -14681,7 +14681,7 @@
         <v>1</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C175" s="4" t="b">
         <v>0</v>
@@ -14690,16 +14690,16 @@
         <v>2004</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G175" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
@@ -14711,7 +14711,7 @@
         <v>1</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C176" s="4" t="b">
         <v>0</v>
@@ -14723,16 +14723,16 @@
         <v>61</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H176" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="I176" s="5" t="s">
         <v>891</v>
-      </c>
-      <c r="I176" s="5" t="s">
-        <v>892</v>
       </c>
       <c r="J176" s="5"/>
       <c r="K176" s="5"/>
@@ -14743,7 +14743,7 @@
         <v>1</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C177" s="4" t="b">
         <v>0</v>
@@ -14755,16 +14755,16 @@
         <v>61</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G177" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I177" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J177" s="5"/>
       <c r="K177" s="5"/>
@@ -14775,7 +14775,7 @@
         <v>1</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C178" s="4" t="b">
         <v>0</v>
@@ -14787,16 +14787,16 @@
         <v>61</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H178" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="I178" s="5" t="s">
         <v>898</v>
-      </c>
-      <c r="I178" s="5" t="s">
-        <v>899</v>
       </c>
       <c r="J178" s="5"/>
       <c r="K178" s="5"/>
@@ -14807,7 +14807,7 @@
         <v>1</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C179" s="4" t="b">
         <v>0</v>
@@ -14819,16 +14819,16 @@
         <v>61</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G179" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I179" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="J179" s="5"/>
       <c r="K179" s="5"/>
@@ -14839,7 +14839,7 @@
         <v>1</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C180" s="4" t="b">
         <v>0</v>
@@ -14848,16 +14848,16 @@
         <v>2003</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G180" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
@@ -14869,7 +14869,7 @@
         <v>1</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C181" s="4" t="b">
         <v>0</v>
@@ -14878,16 +14878,16 @@
         <v>2003</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G181" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
@@ -14899,7 +14899,7 @@
         <v>1</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C182" s="4" t="b">
         <v>0</v>
@@ -14911,13 +14911,13 @@
         <v>61</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G182" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
@@ -14929,7 +14929,7 @@
         <v>1</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C183" s="4" t="b">
         <v>0</v>
@@ -14941,16 +14941,16 @@
         <v>61</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G183" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H183" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="I183" s="5" t="s">
         <v>911</v>
-      </c>
-      <c r="I183" s="5" t="s">
-        <v>912</v>
       </c>
       <c r="J183" s="5"/>
       <c r="K183" s="5"/>
@@ -14961,7 +14961,7 @@
         <v>1</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C184" s="4" t="b">
         <v>0</v>
@@ -14973,16 +14973,16 @@
         <v>61</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G184" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H184" s="5" t="s">
+        <v>914</v>
+      </c>
+      <c r="I184" s="5" t="s">
         <v>915</v>
-      </c>
-      <c r="I184" s="5" t="s">
-        <v>916</v>
       </c>
       <c r="J184" s="5"/>
       <c r="K184" s="5"/>
@@ -14993,7 +14993,7 @@
         <v>1</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="C185" s="4" t="b">
         <v>0</v>
@@ -15005,16 +15005,16 @@
         <v>61</v>
       </c>
       <c r="F185" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H185" s="5" t="s">
         <v>918</v>
       </c>
-      <c r="G185" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="H185" s="5" t="s">
+      <c r="I185" s="5" t="s">
         <v>919</v>
-      </c>
-      <c r="I185" s="5" t="s">
-        <v>920</v>
       </c>
       <c r="J185" s="5"/>
       <c r="K185" s="5"/>
@@ -15025,7 +15025,7 @@
         <v>1</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C186" s="4" t="b">
         <v>0</v>
@@ -15037,16 +15037,16 @@
         <v>61</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G186" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H186" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="I186" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="I186" s="5" t="s">
-        <v>924</v>
       </c>
       <c r="J186" s="5"/>
       <c r="K186" s="5"/>
@@ -15057,7 +15057,7 @@
         <v>1</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C187" s="4" t="b">
         <v>0</v>
@@ -15066,16 +15066,16 @@
         <v>2002</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G187" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I187" s="5"/>
       <c r="J187" s="5"/>
@@ -15087,7 +15087,7 @@
         <v>1</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C188" s="4" t="b">
         <v>0</v>
@@ -15096,16 +15096,16 @@
         <v>2002</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G188" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
@@ -15117,7 +15117,7 @@
         <v>1</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C189" s="4" t="b">
         <v>0</v>
@@ -15126,16 +15126,16 @@
         <v>2002</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G189" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
@@ -15147,7 +15147,7 @@
         <v>1</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C190" s="4" t="b">
         <v>0</v>
@@ -15156,16 +15156,16 @@
         <v>2000</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G190" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
@@ -15177,7 +15177,7 @@
         <v>1</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C191" s="4" t="b">
         <v>0</v>
@@ -15186,16 +15186,16 @@
         <v>1999</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G191" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I191" s="5"/>
       <c r="J191" s="5"/>
@@ -15207,7 +15207,7 @@
         <v>1</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C192" s="4" t="b">
         <v>0</v>
@@ -15216,16 +15216,16 @@
         <v>1999</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G192" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I192" s="5"/>
       <c r="J192" s="5"/>
@@ -15237,7 +15237,7 @@
         <v>1</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C193" s="4" t="b">
         <v>0</v>
@@ -15246,16 +15246,16 @@
         <v>1999</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G193" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I193" s="5"/>
       <c r="J193" s="5"/>
@@ -15267,7 +15267,7 @@
         <v>1</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C194" s="4" t="b">
         <v>0</v>
@@ -15276,16 +15276,16 @@
         <v>1999</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G194" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I194" s="5"/>
       <c r="J194" s="5"/>
@@ -15297,7 +15297,7 @@
         <v>1</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C195" s="4" t="b">
         <v>0</v>
@@ -15306,16 +15306,16 @@
         <v>1999</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G195" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I195" s="5"/>
       <c r="J195" s="5"/>
@@ -15327,7 +15327,7 @@
         <v>1</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C196" s="4" t="b">
         <v>0</v>
@@ -15336,16 +15336,16 @@
         <v>1998</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I196" s="5"/>
       <c r="J196" s="5"/>
@@ -15357,7 +15357,7 @@
         <v>1</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C197" s="4" t="b">
         <v>0</v>
@@ -15366,16 +15366,16 @@
         <v>1997</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G197" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="I197" s="5"/>
       <c r="J197" s="5"/>
@@ -15387,7 +15387,7 @@
         <v>1</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="C198" s="4" t="b">
         <v>0</v>
@@ -15396,16 +15396,16 @@
         <v>1997</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G198" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="I198" s="5"/>
       <c r="J198" s="5"/>
@@ -15417,7 +15417,7 @@
         <v>1</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C199" s="4" t="b">
         <v>0</v>
@@ -15426,16 +15426,16 @@
         <v>1997</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H199" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I199" s="5"/>
       <c r="J199" s="5"/>
